--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,6 +945,2754 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128403964</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98498</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>695772</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6652213</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128403713</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>695845</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6652166</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnagspår i barken på gammal gran.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128403486</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96728</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>53</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>696113</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6652331</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tallåga.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128403368</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106074</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>696248</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6652101</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka självföryngrad ung ask.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128403732</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>695846</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6652175</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128402771</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92682</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>696098</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6652123</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128403010</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101562</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>696201</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6652094</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128403434</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>696113</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6652331</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128403246</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>696215</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6652120</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128403071</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92055</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>696228</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6652121</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På stubbe till grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128403215</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91768</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>696215</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6652120</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På klen granlåga.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128403904</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92293</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>695775</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6652197</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128403356</v>
+      </c>
+      <c r="B16" t="n">
+        <v>103921</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>696248</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6652101</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Enstaka ex.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128403960</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92666</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>695772</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6652213</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128403876</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96728</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>53</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>695806</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6652197</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128402841</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>696097</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6652131</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gnagspår på torrgran.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128403625</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>695859</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6652158</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128402802</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92664</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>696097</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6652131</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128403286</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100658</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>696215</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6652120</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spritt inom biotopen.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128402554</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91376</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>696108</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6652109</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På grenar av granlåga.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128403380</v>
+      </c>
+      <c r="B24" t="n">
+        <v>96728</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>53</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>696224</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6652254</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På tallåga.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128402821</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92682</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>696096</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6652118</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128403975</v>
+      </c>
+      <c r="B26" t="n">
+        <v>100658</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>695772</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6652213</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128403359</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101562</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>696248</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6652101</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128402868</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91376</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>696147</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6652092</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gren av torrgran.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128403599</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92684</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Svartkärrets NR, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>696018</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6652291</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
         <v>128403964</v>
       </c>
       <c r="B4" t="n">
-        <v>98498</v>
+        <v>98500</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>128403486</v>
       </c>
       <c r="B6" t="n">
-        <v>96728</v>
+        <v>96730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,38 +1268,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128403368</v>
+        <v>128403732</v>
       </c>
       <c r="B7" t="n">
-        <v>106074</v>
+        <v>5197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696248</v>
+        <v>695846</v>
       </c>
       <c r="R7" t="n">
-        <v>6652101</v>
+        <v>6652175</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,11 +1348,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,43 +1375,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128403732</v>
+        <v>128403368</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>106076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1419,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695846</v>
+        <v>696248</v>
       </c>
       <c r="R8" t="n">
-        <v>6652175</v>
+        <v>6652101</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,6 +1450,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,7 +1485,7 @@
         <v>128402771</v>
       </c>
       <c r="B9" t="n">
-        <v>92682</v>
+        <v>92684</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>128403010</v>
       </c>
       <c r="B10" t="n">
-        <v>101562</v>
+        <v>101564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128403246</v>
+        <v>128403071</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>92057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,32 +1803,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1836,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696215</v>
+        <v>696228</v>
       </c>
       <c r="R12" t="n">
-        <v>6652120</v>
+        <v>6652121</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1872,6 +1866,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På stubbe till grov granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128403071</v>
+        <v>128403246</v>
       </c>
       <c r="B13" t="n">
-        <v>92055</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,26 +1909,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1937,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696228</v>
+        <v>696215</v>
       </c>
       <c r="R13" t="n">
-        <v>6652121</v>
+        <v>6652120</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1973,11 +1978,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På stubbe till grov granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,7 +2008,7 @@
         <v>128403215</v>
       </c>
       <c r="B14" t="n">
-        <v>91768</v>
+        <v>91770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>128403904</v>
       </c>
       <c r="B15" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>128403356</v>
       </c>
       <c r="B16" t="n">
-        <v>103921</v>
+        <v>103923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>128403960</v>
       </c>
       <c r="B17" t="n">
-        <v>92666</v>
+        <v>92668</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128403876</v>
       </c>
       <c r="B18" t="n">
-        <v>96728</v>
+        <v>96730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>128402802</v>
       </c>
       <c r="B21" t="n">
-        <v>92664</v>
+        <v>92666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>128403286</v>
       </c>
       <c r="B22" t="n">
-        <v>100658</v>
+        <v>100660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>128402554</v>
       </c>
       <c r="B23" t="n">
-        <v>91376</v>
+        <v>91378</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>128403380</v>
       </c>
       <c r="B24" t="n">
-        <v>96728</v>
+        <v>96730</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128402821</v>
       </c>
       <c r="B25" t="n">
-        <v>92682</v>
+        <v>92684</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128403975</v>
+        <v>128403359</v>
       </c>
       <c r="B26" t="n">
-        <v>100658</v>
+        <v>101564</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,21 +3287,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695772</v>
+        <v>696248</v>
       </c>
       <c r="R26" t="n">
-        <v>6652213</v>
+        <v>6652101</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3378,10 +3378,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128403359</v>
+        <v>128403975</v>
       </c>
       <c r="B27" t="n">
-        <v>101562</v>
+        <v>100660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696248</v>
+        <v>695772</v>
       </c>
       <c r="R27" t="n">
-        <v>6652101</v>
+        <v>6652213</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3483,7 +3483,7 @@
         <v>128402868</v>
       </c>
       <c r="B28" t="n">
-        <v>91376</v>
+        <v>91378</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>128403599</v>
       </c>
       <c r="B29" t="n">
-        <v>92684</v>
+        <v>92686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
         <v>128403964</v>
       </c>
       <c r="B4" t="n">
-        <v>98500</v>
+        <v>98593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,43 +1049,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403713</v>
+        <v>128403486</v>
       </c>
       <c r="B5" t="n">
-        <v>4779</v>
+        <v>96823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1093,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695845</v>
+        <v>696113</v>
       </c>
       <c r="R5" t="n">
-        <v>6652166</v>
+        <v>6652331</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,7 +1128,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal gran.</t>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,38 +1156,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403486</v>
+        <v>128403713</v>
       </c>
       <c r="B6" t="n">
-        <v>96730</v>
+        <v>4779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696113</v>
+        <v>695845</v>
       </c>
       <c r="R6" t="n">
-        <v>6652331</v>
+        <v>6652166</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tallåga.</t>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1378,7 +1378,7 @@
         <v>128403368</v>
       </c>
       <c r="B8" t="n">
-        <v>106076</v>
+        <v>106169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>128402771</v>
       </c>
       <c r="B9" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>128403010</v>
       </c>
       <c r="B10" t="n">
-        <v>101564</v>
+        <v>101657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128403071</v>
+        <v>128403246</v>
       </c>
       <c r="B12" t="n">
-        <v>92057</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,26 +1803,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1830,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696228</v>
+        <v>696215</v>
       </c>
       <c r="R12" t="n">
-        <v>6652121</v>
+        <v>6652120</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1868,11 +1874,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På stubbe till grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1891,17 +1892,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128403246</v>
+        <v>128403071</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>92149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,32 +1910,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1942,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696215</v>
+        <v>696228</v>
       </c>
       <c r="R13" t="n">
-        <v>6652120</v>
+        <v>6652121</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1978,6 +1973,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På stubbe till grov granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128403215</v>
+        <v>128403904</v>
       </c>
       <c r="B14" t="n">
-        <v>91770</v>
+        <v>92387</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4217</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696215</v>
+        <v>695775</v>
       </c>
       <c r="R14" t="n">
-        <v>6652120</v>
+        <v>6652197</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2079,11 +2079,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På klen granlåga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128403904</v>
+        <v>128403215</v>
       </c>
       <c r="B15" t="n">
-        <v>92295</v>
+        <v>91862</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,21 +2117,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2144,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695775</v>
+        <v>696215</v>
       </c>
       <c r="R15" t="n">
-        <v>6652197</v>
+        <v>6652120</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2187,6 +2182,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På klen granlåga.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
         <v>128403356</v>
       </c>
       <c r="B16" t="n">
-        <v>103923</v>
+        <v>104016</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>128403960</v>
       </c>
       <c r="B17" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128403876</v>
       </c>
       <c r="B18" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>128402802</v>
       </c>
       <c r="B21" t="n">
-        <v>92666</v>
+        <v>92758</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>128403286</v>
       </c>
       <c r="B22" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2965,7 +2965,7 @@
         <v>128402554</v>
       </c>
       <c r="B23" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>128403380</v>
       </c>
       <c r="B24" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128402821</v>
       </c>
       <c r="B25" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128403359</v>
+        <v>128403975</v>
       </c>
       <c r="B26" t="n">
-        <v>101564</v>
+        <v>100753</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,21 +3287,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696248</v>
+        <v>695772</v>
       </c>
       <c r="R26" t="n">
-        <v>6652101</v>
+        <v>6652213</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3378,10 +3378,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128403975</v>
+        <v>128403359</v>
       </c>
       <c r="B27" t="n">
-        <v>100660</v>
+        <v>101657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695772</v>
+        <v>696248</v>
       </c>
       <c r="R27" t="n">
-        <v>6652213</v>
+        <v>6652101</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3483,7 +3483,7 @@
         <v>128402868</v>
       </c>
       <c r="B28" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>128403599</v>
       </c>
       <c r="B29" t="n">
-        <v>92686</v>
+        <v>92778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -1049,38 +1049,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403486</v>
+        <v>128403732</v>
       </c>
       <c r="B5" t="n">
-        <v>96823</v>
+        <v>5197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696113</v>
+        <v>695846</v>
       </c>
       <c r="R5" t="n">
-        <v>6652331</v>
+        <v>6652175</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,11 +1129,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,43 +1156,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403713</v>
+        <v>128403368</v>
       </c>
       <c r="B6" t="n">
-        <v>4779</v>
+        <v>106169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695845</v>
+        <v>696248</v>
       </c>
       <c r="R6" t="n">
-        <v>6652166</v>
+        <v>6652101</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1240,7 +1235,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal gran.</t>
+          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,43 +1263,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128403732</v>
+        <v>128403486</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>96823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1312,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695846</v>
+        <v>696113</v>
       </c>
       <c r="R7" t="n">
-        <v>6652175</v>
+        <v>6652331</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,6 +1338,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,38 +1370,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128403368</v>
+        <v>128403713</v>
       </c>
       <c r="B8" t="n">
-        <v>106169</v>
+        <v>4779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696248</v>
+        <v>695845</v>
       </c>
       <c r="R8" t="n">
-        <v>6652101</v>
+        <v>6652166</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka självföryngrad ung ask.</t>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128402771</v>
+        <v>128403010</v>
       </c>
       <c r="B9" t="n">
-        <v>92776</v>
+        <v>101657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,26 +1493,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1520,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696098</v>
+        <v>696201</v>
       </c>
       <c r="R9" t="n">
-        <v>6652123</v>
+        <v>6652094</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1583,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128403010</v>
+        <v>128402771</v>
       </c>
       <c r="B10" t="n">
-        <v>101657</v>
+        <v>92776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,27 +1595,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696201</v>
+        <v>696098</v>
       </c>
       <c r="R10" t="n">
-        <v>6652094</v>
+        <v>6652123</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128403246</v>
+        <v>128403071</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>92149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,32 +1803,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1836,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696215</v>
+        <v>696228</v>
       </c>
       <c r="R12" t="n">
-        <v>6652120</v>
+        <v>6652121</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1874,6 +1868,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På stubbe till grov granlåga.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1892,17 +1891,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128403071</v>
+        <v>128403246</v>
       </c>
       <c r="B13" t="n">
-        <v>92149</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,26 +1909,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1937,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696228</v>
+        <v>696215</v>
       </c>
       <c r="R13" t="n">
-        <v>6652121</v>
+        <v>6652120</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1975,11 +1980,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På stubbe till grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -1049,43 +1049,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403732</v>
+        <v>128403486</v>
       </c>
       <c r="B5" t="n">
-        <v>5197</v>
+        <v>96823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1093,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695846</v>
+        <v>696113</v>
       </c>
       <c r="R5" t="n">
-        <v>6652175</v>
+        <v>6652331</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1129,6 +1124,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,38 +1156,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403368</v>
+        <v>128403713</v>
       </c>
       <c r="B6" t="n">
-        <v>106169</v>
+        <v>4779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696248</v>
+        <v>695845</v>
       </c>
       <c r="R6" t="n">
-        <v>6652101</v>
+        <v>6652166</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka självföryngrad ung ask.</t>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,38 +1268,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128403486</v>
+        <v>128403732</v>
       </c>
       <c r="B7" t="n">
-        <v>96823</v>
+        <v>5197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696113</v>
+        <v>695846</v>
       </c>
       <c r="R7" t="n">
-        <v>6652331</v>
+        <v>6652175</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1338,11 +1348,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,43 +1375,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128403713</v>
+        <v>128403368</v>
       </c>
       <c r="B8" t="n">
-        <v>4779</v>
+        <v>106169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695845</v>
+        <v>696248</v>
       </c>
       <c r="R8" t="n">
-        <v>6652166</v>
+        <v>6652101</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal gran.</t>
+          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128403071</v>
+        <v>128403246</v>
       </c>
       <c r="B12" t="n">
-        <v>92149</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,26 +1803,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1830,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696228</v>
+        <v>696215</v>
       </c>
       <c r="R12" t="n">
-        <v>6652121</v>
+        <v>6652120</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1868,11 +1874,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På stubbe till grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1891,17 +1892,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128403246</v>
+        <v>128403071</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>92149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,32 +1910,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1942,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696215</v>
+        <v>696228</v>
       </c>
       <c r="R13" t="n">
-        <v>6652120</v>
+        <v>6652121</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1980,6 +1975,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På stubbe till grov granlåga.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1998,17 +1998,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128403904</v>
+        <v>128403215</v>
       </c>
       <c r="B14" t="n">
-        <v>92387</v>
+        <v>91862</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695775</v>
+        <v>696215</v>
       </c>
       <c r="R14" t="n">
-        <v>6652197</v>
+        <v>6652120</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,6 +2081,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På klen granlåga.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2099,17 +2104,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128403215</v>
+        <v>128403904</v>
       </c>
       <c r="B15" t="n">
-        <v>91862</v>
+        <v>92387</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,21 +2122,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4217</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2144,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696215</v>
+        <v>695775</v>
       </c>
       <c r="R15" t="n">
-        <v>6652120</v>
+        <v>6652197</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2182,11 +2187,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På klen granlåga.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
         <v>128403964</v>
       </c>
       <c r="B4" t="n">
-        <v>98593</v>
+        <v>98607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,38 +1049,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403486</v>
+        <v>128403732</v>
       </c>
       <c r="B5" t="n">
-        <v>96823</v>
+        <v>5197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696113</v>
+        <v>695846</v>
       </c>
       <c r="R5" t="n">
-        <v>6652331</v>
+        <v>6652175</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,11 +1129,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,43 +1156,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403713</v>
+        <v>128403368</v>
       </c>
       <c r="B6" t="n">
-        <v>4779</v>
+        <v>106190</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695845</v>
+        <v>696248</v>
       </c>
       <c r="R6" t="n">
-        <v>6652166</v>
+        <v>6652101</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1240,7 +1235,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal gran.</t>
+          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,43 +1263,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128403732</v>
+        <v>128403486</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>96835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1312,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695846</v>
+        <v>696113</v>
       </c>
       <c r="R7" t="n">
-        <v>6652175</v>
+        <v>6652331</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,6 +1338,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,38 +1370,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128403368</v>
+        <v>128403713</v>
       </c>
       <c r="B8" t="n">
-        <v>106169</v>
+        <v>4779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696248</v>
+        <v>695845</v>
       </c>
       <c r="R8" t="n">
-        <v>6652101</v>
+        <v>6652166</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka självföryngrad ung ask.</t>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128403010</v>
+        <v>128402771</v>
       </c>
       <c r="B9" t="n">
-        <v>101657</v>
+        <v>92788</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,27 +1493,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1521,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696201</v>
+        <v>696098</v>
       </c>
       <c r="R9" t="n">
-        <v>6652094</v>
+        <v>6652123</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1584,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128402771</v>
+        <v>128403010</v>
       </c>
       <c r="B10" t="n">
-        <v>92776</v>
+        <v>101673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,26 +1594,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696098</v>
+        <v>696201</v>
       </c>
       <c r="R10" t="n">
-        <v>6652123</v>
+        <v>6652094</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128403246</v>
+        <v>128403071</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>92161</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,32 +1803,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1836,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696215</v>
+        <v>696228</v>
       </c>
       <c r="R12" t="n">
-        <v>6652120</v>
+        <v>6652121</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1874,6 +1868,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På stubbe till grov granlåga.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1892,17 +1891,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128403071</v>
+        <v>128403246</v>
       </c>
       <c r="B13" t="n">
-        <v>92149</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,26 +1909,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1937,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696228</v>
+        <v>696215</v>
       </c>
       <c r="R13" t="n">
-        <v>6652121</v>
+        <v>6652120</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1975,11 +1980,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På stubbe till grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
         <v>128403215</v>
       </c>
       <c r="B14" t="n">
-        <v>91862</v>
+        <v>91874</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>128403904</v>
       </c>
       <c r="B15" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>128403356</v>
       </c>
       <c r="B16" t="n">
-        <v>104016</v>
+        <v>104036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>128403960</v>
       </c>
       <c r="B17" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128403876</v>
       </c>
       <c r="B18" t="n">
-        <v>96823</v>
+        <v>96835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>128402802</v>
       </c>
       <c r="B21" t="n">
-        <v>92758</v>
+        <v>92770</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>128403286</v>
       </c>
       <c r="B22" t="n">
-        <v>100753</v>
+        <v>100768</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>128402554</v>
       </c>
       <c r="B23" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3071,7 +3071,7 @@
         <v>128403380</v>
       </c>
       <c r="B24" t="n">
-        <v>96823</v>
+        <v>96835</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128402821</v>
       </c>
       <c r="B25" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>128403975</v>
       </c>
       <c r="B26" t="n">
-        <v>100753</v>
+        <v>100768</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128403359</v>
       </c>
       <c r="B27" t="n">
-        <v>101657</v>
+        <v>101673</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128402868</v>
+        <v>128403599</v>
       </c>
       <c r="B28" t="n">
-        <v>91470</v>
+        <v>92790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,25 +3491,33 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3518,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696147</v>
+        <v>696018</v>
       </c>
       <c r="R28" t="n">
-        <v>6652092</v>
+        <v>6652291</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3554,11 +3562,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gren av torrgran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3586,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128403599</v>
+        <v>128402868</v>
       </c>
       <c r="B29" t="n">
-        <v>92778</v>
+        <v>91482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3597,33 +3600,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3632,10 +3627,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696018</v>
+        <v>696147</v>
       </c>
       <c r="R29" t="n">
-        <v>6652291</v>
+        <v>6652092</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3668,6 +3663,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gren av torrgran.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -1049,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403732</v>
+        <v>128403713</v>
       </c>
       <c r="B5" t="n">
-        <v>5197</v>
+        <v>4779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,21 +1060,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695846</v>
+        <v>695845</v>
       </c>
       <c r="R5" t="n">
-        <v>6652175</v>
+        <v>6652166</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1129,6 +1129,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,32 +1161,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403368</v>
+        <v>128403486</v>
       </c>
       <c r="B6" t="n">
-        <v>106190</v>
+        <v>96835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696248</v>
+        <v>696113</v>
       </c>
       <c r="R6" t="n">
-        <v>6652101</v>
+        <v>6652331</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka självföryngrad ung ask.</t>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,38 +1268,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128403486</v>
+        <v>128403732</v>
       </c>
       <c r="B7" t="n">
-        <v>96835</v>
+        <v>5197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696113</v>
+        <v>695846</v>
       </c>
       <c r="R7" t="n">
-        <v>6652331</v>
+        <v>6652175</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1338,11 +1348,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,43 +1375,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128403713</v>
+        <v>128403368</v>
       </c>
       <c r="B8" t="n">
-        <v>4779</v>
+        <v>106190</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695845</v>
+        <v>696248</v>
       </c>
       <c r="R8" t="n">
-        <v>6652166</v>
+        <v>6652101</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal gran.</t>
+          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
         <v>128403964</v>
       </c>
       <c r="B4" t="n">
-        <v>98607</v>
+        <v>98610</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,43 +1049,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403713</v>
+        <v>128403486</v>
       </c>
       <c r="B5" t="n">
-        <v>4779</v>
+        <v>96837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1093,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695845</v>
+        <v>696113</v>
       </c>
       <c r="R5" t="n">
-        <v>6652166</v>
+        <v>6652331</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,7 +1128,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal gran.</t>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,38 +1156,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403486</v>
+        <v>128403713</v>
       </c>
       <c r="B6" t="n">
-        <v>96835</v>
+        <v>4779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696113</v>
+        <v>695845</v>
       </c>
       <c r="R6" t="n">
-        <v>6652331</v>
+        <v>6652166</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tallåga.</t>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1378,7 +1378,7 @@
         <v>128403368</v>
       </c>
       <c r="B8" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>128402771</v>
       </c>
       <c r="B9" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>128403010</v>
       </c>
       <c r="B10" t="n">
-        <v>101673</v>
+        <v>101678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128403071</v>
+        <v>128403246</v>
       </c>
       <c r="B12" t="n">
-        <v>92161</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,26 +1803,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1830,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696228</v>
+        <v>696215</v>
       </c>
       <c r="R12" t="n">
-        <v>6652121</v>
+        <v>6652120</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1868,11 +1874,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På stubbe till grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1891,17 +1892,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128403246</v>
+        <v>128403071</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>92163</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,32 +1910,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1942,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696215</v>
+        <v>696228</v>
       </c>
       <c r="R13" t="n">
-        <v>6652120</v>
+        <v>6652121</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1980,6 +1975,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På stubbe till grov granlåga.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1998,17 +1998,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128403215</v>
+        <v>128403904</v>
       </c>
       <c r="B14" t="n">
-        <v>91874</v>
+        <v>92401</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4217</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696215</v>
+        <v>695775</v>
       </c>
       <c r="R14" t="n">
-        <v>6652120</v>
+        <v>6652197</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,11 +2081,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På klen granlåga.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2104,17 +2099,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128403904</v>
+        <v>128403215</v>
       </c>
       <c r="B15" t="n">
-        <v>92399</v>
+        <v>91876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,21 +2117,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2144,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695775</v>
+        <v>696215</v>
       </c>
       <c r="R15" t="n">
-        <v>6652197</v>
+        <v>6652120</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2187,6 +2182,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På klen granlåga.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
         <v>128403356</v>
       </c>
       <c r="B16" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>128403960</v>
       </c>
       <c r="B17" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128403876</v>
       </c>
       <c r="B18" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>128402802</v>
       </c>
       <c r="B21" t="n">
-        <v>92770</v>
+        <v>92772</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>128403286</v>
       </c>
       <c r="B22" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>128402554</v>
       </c>
       <c r="B23" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>128403380</v>
       </c>
       <c r="B24" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128402821</v>
       </c>
       <c r="B25" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>128403975</v>
       </c>
       <c r="B26" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128403359</v>
       </c>
       <c r="B27" t="n">
-        <v>101673</v>
+        <v>101678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128403599</v>
+        <v>128402868</v>
       </c>
       <c r="B28" t="n">
-        <v>92790</v>
+        <v>91484</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,33 +3491,25 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3526,10 +3518,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696018</v>
+        <v>696147</v>
       </c>
       <c r="R28" t="n">
-        <v>6652291</v>
+        <v>6652092</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3562,6 +3554,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gren av torrgran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3586,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128402868</v>
+        <v>128403599</v>
       </c>
       <c r="B29" t="n">
-        <v>91482</v>
+        <v>92792</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,25 +3597,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3627,10 +3632,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696147</v>
+        <v>696018</v>
       </c>
       <c r="R29" t="n">
-        <v>6652092</v>
+        <v>6652291</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3663,11 +3668,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gren av torrgran.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
         <v>128403964</v>
       </c>
       <c r="B4" t="n">
-        <v>98610</v>
+        <v>98613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,38 +1049,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403486</v>
+        <v>128403713</v>
       </c>
       <c r="B5" t="n">
-        <v>96837</v>
+        <v>4779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696113</v>
+        <v>695845</v>
       </c>
       <c r="R5" t="n">
-        <v>6652331</v>
+        <v>6652166</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,7 +1133,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tallåga.</t>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403713</v>
+        <v>128403732</v>
       </c>
       <c r="B6" t="n">
-        <v>4779</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,21 +1172,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695845</v>
+        <v>695846</v>
       </c>
       <c r="R6" t="n">
-        <v>6652166</v>
+        <v>6652175</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1236,11 +1241,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,43 +1268,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128403732</v>
+        <v>128403368</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>106211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695846</v>
+        <v>696248</v>
       </c>
       <c r="R7" t="n">
-        <v>6652175</v>
+        <v>6652101</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,6 +1343,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,32 +1375,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128403368</v>
+        <v>128403486</v>
       </c>
       <c r="B8" t="n">
-        <v>106202</v>
+        <v>96837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696248</v>
+        <v>696113</v>
       </c>
       <c r="R8" t="n">
-        <v>6652101</v>
+        <v>6652331</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka självföryngrad ung ask.</t>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128402771</v>
+        <v>128403010</v>
       </c>
       <c r="B9" t="n">
-        <v>92790</v>
+        <v>101684</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,26 +1493,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1520,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696098</v>
+        <v>696201</v>
       </c>
       <c r="R9" t="n">
-        <v>6652123</v>
+        <v>6652094</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1583,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128403010</v>
+        <v>128402771</v>
       </c>
       <c r="B10" t="n">
-        <v>101678</v>
+        <v>92790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,27 +1595,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696201</v>
+        <v>696098</v>
       </c>
       <c r="R10" t="n">
-        <v>6652094</v>
+        <v>6652123</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128403246</v>
+        <v>128403071</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>92163</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,32 +1803,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1836,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696215</v>
+        <v>696228</v>
       </c>
       <c r="R12" t="n">
-        <v>6652120</v>
+        <v>6652121</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1874,6 +1868,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På stubbe till grov granlåga.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1892,17 +1891,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128403071</v>
+        <v>128403246</v>
       </c>
       <c r="B13" t="n">
-        <v>92163</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,26 +1909,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1937,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696228</v>
+        <v>696215</v>
       </c>
       <c r="R13" t="n">
-        <v>6652121</v>
+        <v>6652120</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1975,11 +1980,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På stubbe till grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
         <v>128403356</v>
       </c>
       <c r="B16" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2746,45 +2746,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128402802</v>
+        <v>128403286</v>
       </c>
       <c r="B21" t="n">
-        <v>92772</v>
+        <v>100779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2792,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696097</v>
+        <v>696215</v>
       </c>
       <c r="R21" t="n">
-        <v>6652131</v>
+        <v>6652120</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2830,6 +2823,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spritt inom biotopen.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2848,45 +2846,52 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128403286</v>
+        <v>128402802</v>
       </c>
       <c r="B22" t="n">
-        <v>100773</v>
+        <v>92772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2894,10 +2899,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696215</v>
+        <v>696097</v>
       </c>
       <c r="R22" t="n">
-        <v>6652120</v>
+        <v>6652131</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2932,11 +2937,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spritt inom biotopen.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3279,7 +3279,7 @@
         <v>128403975</v>
       </c>
       <c r="B26" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128403359</v>
       </c>
       <c r="B27" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128402868</v>
+        <v>128403599</v>
       </c>
       <c r="B28" t="n">
-        <v>91484</v>
+        <v>92792</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,25 +3491,33 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3518,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696147</v>
+        <v>696018</v>
       </c>
       <c r="R28" t="n">
-        <v>6652092</v>
+        <v>6652291</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3554,11 +3562,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gren av torrgran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3586,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128403599</v>
+        <v>128402868</v>
       </c>
       <c r="B29" t="n">
-        <v>92792</v>
+        <v>91484</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3597,33 +3600,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3632,10 +3627,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696018</v>
+        <v>696147</v>
       </c>
       <c r="R29" t="n">
-        <v>6652291</v>
+        <v>6652092</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3668,6 +3663,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gren av torrgran.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -1049,43 +1049,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403713</v>
+        <v>128403368</v>
       </c>
       <c r="B5" t="n">
-        <v>4779</v>
+        <v>106211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1093,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695845</v>
+        <v>696248</v>
       </c>
       <c r="R5" t="n">
-        <v>6652166</v>
+        <v>6652101</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,7 +1128,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal gran.</t>
+          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,43 +1156,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403732</v>
+        <v>128403486</v>
       </c>
       <c r="B6" t="n">
-        <v>5197</v>
+        <v>96837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1205,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695846</v>
+        <v>696113</v>
       </c>
       <c r="R6" t="n">
-        <v>6652175</v>
+        <v>6652331</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1241,6 +1231,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,38 +1263,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128403368</v>
+        <v>128403713</v>
       </c>
       <c r="B7" t="n">
-        <v>106211</v>
+        <v>4779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696248</v>
+        <v>695845</v>
       </c>
       <c r="R7" t="n">
-        <v>6652101</v>
+        <v>6652166</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Enstaka självföryngrad ung ask.</t>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,38 +1375,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128403486</v>
+        <v>128403732</v>
       </c>
       <c r="B8" t="n">
-        <v>96837</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696113</v>
+        <v>695846</v>
       </c>
       <c r="R8" t="n">
-        <v>6652331</v>
+        <v>6652175</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,11 +1455,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2746,38 +2746,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128403286</v>
+        <v>128402802</v>
       </c>
       <c r="B21" t="n">
-        <v>100779</v>
+        <v>92772</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2785,10 +2792,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696215</v>
+        <v>696097</v>
       </c>
       <c r="R21" t="n">
-        <v>6652120</v>
+        <v>6652131</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2823,11 +2830,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spritt inom biotopen.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2846,52 +2848,45 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128402802</v>
+        <v>128403286</v>
       </c>
       <c r="B22" t="n">
-        <v>92772</v>
+        <v>100779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2899,10 +2894,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696097</v>
+        <v>696215</v>
       </c>
       <c r="R22" t="n">
-        <v>6652131</v>
+        <v>6652120</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2937,6 +2932,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spritt inom biotopen.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
         <v>128403964</v>
       </c>
       <c r="B4" t="n">
-        <v>98613</v>
+        <v>98614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,32 +1049,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403368</v>
+        <v>128403486</v>
       </c>
       <c r="B5" t="n">
-        <v>106211</v>
+        <v>96838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696248</v>
+        <v>696113</v>
       </c>
       <c r="R5" t="n">
-        <v>6652101</v>
+        <v>6652331</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka självföryngrad ung ask.</t>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,38 +1156,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403486</v>
+        <v>128403713</v>
       </c>
       <c r="B6" t="n">
-        <v>96837</v>
+        <v>4779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696113</v>
+        <v>695845</v>
       </c>
       <c r="R6" t="n">
-        <v>6652331</v>
+        <v>6652166</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tallåga.</t>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128403713</v>
+        <v>128403732</v>
       </c>
       <c r="B7" t="n">
-        <v>4779</v>
+        <v>5197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,21 +1279,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695845</v>
+        <v>695846</v>
       </c>
       <c r="R7" t="n">
-        <v>6652166</v>
+        <v>6652175</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,11 +1348,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,43 +1375,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128403732</v>
+        <v>128403368</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>106216</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1419,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695846</v>
+        <v>696248</v>
       </c>
       <c r="R8" t="n">
-        <v>6652175</v>
+        <v>6652101</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,6 +1450,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128403010</v>
+        <v>128402771</v>
       </c>
       <c r="B9" t="n">
-        <v>101684</v>
+        <v>92791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,27 +1493,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1521,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696201</v>
+        <v>696098</v>
       </c>
       <c r="R9" t="n">
-        <v>6652094</v>
+        <v>6652123</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1584,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128402771</v>
+        <v>128403010</v>
       </c>
       <c r="B10" t="n">
-        <v>92790</v>
+        <v>101685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,26 +1594,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696098</v>
+        <v>696201</v>
       </c>
       <c r="R10" t="n">
-        <v>6652123</v>
+        <v>6652094</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128403071</v>
+        <v>128403246</v>
       </c>
       <c r="B12" t="n">
-        <v>92163</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,26 +1803,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1830,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696228</v>
+        <v>696215</v>
       </c>
       <c r="R12" t="n">
-        <v>6652121</v>
+        <v>6652120</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1868,11 +1874,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På stubbe till grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1891,17 +1892,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128403246</v>
+        <v>128403071</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>92164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,32 +1910,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1942,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696215</v>
+        <v>696228</v>
       </c>
       <c r="R13" t="n">
-        <v>6652120</v>
+        <v>6652121</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1980,6 +1975,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På stubbe till grov granlåga.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1998,17 +1998,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128403904</v>
+        <v>128403215</v>
       </c>
       <c r="B14" t="n">
-        <v>92401</v>
+        <v>91877</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695775</v>
+        <v>696215</v>
       </c>
       <c r="R14" t="n">
-        <v>6652197</v>
+        <v>6652120</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,6 +2081,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På klen granlåga.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2099,17 +2104,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128403215</v>
+        <v>128403904</v>
       </c>
       <c r="B15" t="n">
-        <v>91876</v>
+        <v>92402</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,21 +2122,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4217</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2144,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696215</v>
+        <v>695775</v>
       </c>
       <c r="R15" t="n">
-        <v>6652120</v>
+        <v>6652197</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2182,11 +2187,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På klen granlåga.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
         <v>128403356</v>
       </c>
       <c r="B16" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>128403960</v>
       </c>
       <c r="B17" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128403876</v>
       </c>
       <c r="B18" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2746,45 +2746,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128402802</v>
+        <v>128403286</v>
       </c>
       <c r="B21" t="n">
-        <v>92772</v>
+        <v>100780</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2792,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696097</v>
+        <v>696215</v>
       </c>
       <c r="R21" t="n">
-        <v>6652131</v>
+        <v>6652120</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2830,6 +2823,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spritt inom biotopen.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2848,45 +2846,52 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128403286</v>
+        <v>128402802</v>
       </c>
       <c r="B22" t="n">
-        <v>100779</v>
+        <v>92773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2894,10 +2899,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696215</v>
+        <v>696097</v>
       </c>
       <c r="R22" t="n">
-        <v>6652120</v>
+        <v>6652131</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2932,11 +2937,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spritt inom biotopen.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2965,7 +2965,7 @@
         <v>128402554</v>
       </c>
       <c r="B23" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>128403380</v>
       </c>
       <c r="B24" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128402821</v>
       </c>
       <c r="B25" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>128403975</v>
       </c>
       <c r="B26" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128403359</v>
       </c>
       <c r="B27" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128403599</v>
+        <v>128402868</v>
       </c>
       <c r="B28" t="n">
-        <v>92792</v>
+        <v>91485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,33 +3491,25 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3526,10 +3518,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696018</v>
+        <v>696147</v>
       </c>
       <c r="R28" t="n">
-        <v>6652291</v>
+        <v>6652092</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3562,6 +3554,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gren av torrgran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3586,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128402868</v>
+        <v>128403599</v>
       </c>
       <c r="B29" t="n">
-        <v>91484</v>
+        <v>92793</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,25 +3597,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3627,10 +3632,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696147</v>
+        <v>696018</v>
       </c>
       <c r="R29" t="n">
-        <v>6652092</v>
+        <v>6652291</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3663,11 +3668,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gren av torrgran.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128403246</v>
+        <v>128403071</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>92164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,32 +1803,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1836,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696215</v>
+        <v>696228</v>
       </c>
       <c r="R12" t="n">
-        <v>6652120</v>
+        <v>6652121</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1874,6 +1868,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På stubbe till grov granlåga.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1892,17 +1891,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128403071</v>
+        <v>128403246</v>
       </c>
       <c r="B13" t="n">
-        <v>92164</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,26 +1909,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1937,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696228</v>
+        <v>696215</v>
       </c>
       <c r="R13" t="n">
-        <v>6652121</v>
+        <v>6652120</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1975,11 +1980,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På stubbe till grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
         <v>128403964</v>
       </c>
       <c r="B4" t="n">
-        <v>98614</v>
+        <v>98641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>128403486</v>
       </c>
       <c r="B5" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1268,43 +1268,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128403732</v>
+        <v>128403368</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>106244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695846</v>
+        <v>696248</v>
       </c>
       <c r="R7" t="n">
-        <v>6652175</v>
+        <v>6652101</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,6 +1343,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,38 +1375,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128403368</v>
+        <v>128403732</v>
       </c>
       <c r="B8" t="n">
-        <v>106216</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696248</v>
+        <v>695846</v>
       </c>
       <c r="R8" t="n">
-        <v>6652101</v>
+        <v>6652175</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,11 +1455,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128402771</v>
+        <v>128403010</v>
       </c>
       <c r="B9" t="n">
-        <v>92791</v>
+        <v>101712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,26 +1493,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1520,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696098</v>
+        <v>696201</v>
       </c>
       <c r="R9" t="n">
-        <v>6652123</v>
+        <v>6652094</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1583,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128403010</v>
+        <v>128402771</v>
       </c>
       <c r="B10" t="n">
-        <v>101685</v>
+        <v>92818</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,27 +1595,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696201</v>
+        <v>696098</v>
       </c>
       <c r="R10" t="n">
-        <v>6652094</v>
+        <v>6652123</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1795,7 +1795,7 @@
         <v>128403071</v>
       </c>
       <c r="B12" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128403215</v>
+        <v>128403904</v>
       </c>
       <c r="B14" t="n">
-        <v>91877</v>
+        <v>92429</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4217</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696215</v>
+        <v>695775</v>
       </c>
       <c r="R14" t="n">
-        <v>6652120</v>
+        <v>6652197</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,11 +2081,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På klen granlåga.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2104,17 +2099,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128403904</v>
+        <v>128403215</v>
       </c>
       <c r="B15" t="n">
-        <v>92402</v>
+        <v>91904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,21 +2117,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2144,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695775</v>
+        <v>696215</v>
       </c>
       <c r="R15" t="n">
-        <v>6652197</v>
+        <v>6652120</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2187,6 +2182,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På klen granlåga.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
         <v>128403356</v>
       </c>
       <c r="B16" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>128403960</v>
       </c>
       <c r="B17" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128403876</v>
       </c>
       <c r="B18" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2746,38 +2746,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128403286</v>
+        <v>128402802</v>
       </c>
       <c r="B21" t="n">
-        <v>100780</v>
+        <v>92800</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2785,10 +2792,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696215</v>
+        <v>696097</v>
       </c>
       <c r="R21" t="n">
-        <v>6652120</v>
+        <v>6652131</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2823,11 +2830,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spritt inom biotopen.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2846,52 +2848,45 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128402802</v>
+        <v>128403286</v>
       </c>
       <c r="B22" t="n">
-        <v>92773</v>
+        <v>100807</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2899,10 +2894,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696097</v>
+        <v>696215</v>
       </c>
       <c r="R22" t="n">
-        <v>6652131</v>
+        <v>6652120</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2937,6 +2932,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spritt inom biotopen.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2965,7 +2965,7 @@
         <v>128402554</v>
       </c>
       <c r="B23" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>128403380</v>
       </c>
       <c r="B24" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128402821</v>
       </c>
       <c r="B25" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>128403975</v>
       </c>
       <c r="B26" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>128403359</v>
       </c>
       <c r="B27" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>128402868</v>
       </c>
       <c r="B28" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>128403599</v>
       </c>
       <c r="B29" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -1049,38 +1049,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403486</v>
+        <v>128403713</v>
       </c>
       <c r="B5" t="n">
-        <v>96865</v>
+        <v>4779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696113</v>
+        <v>695845</v>
       </c>
       <c r="R5" t="n">
-        <v>6652331</v>
+        <v>6652166</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,7 +1133,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tallåga.</t>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,43 +1161,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403713</v>
+        <v>128403486</v>
       </c>
       <c r="B6" t="n">
-        <v>4779</v>
+        <v>96865</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695845</v>
+        <v>696113</v>
       </c>
       <c r="R6" t="n">
-        <v>6652166</v>
+        <v>6652331</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal gran.</t>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,38 +1268,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128403368</v>
+        <v>128403732</v>
       </c>
       <c r="B7" t="n">
-        <v>106244</v>
+        <v>5197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696248</v>
+        <v>695846</v>
       </c>
       <c r="R7" t="n">
-        <v>6652101</v>
+        <v>6652175</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,11 +1348,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,43 +1375,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128403732</v>
+        <v>128403368</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>106244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1419,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695846</v>
+        <v>696248</v>
       </c>
       <c r="R8" t="n">
-        <v>6652175</v>
+        <v>6652101</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,6 +1450,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128403010</v>
+        <v>128402771</v>
       </c>
       <c r="B9" t="n">
-        <v>101712</v>
+        <v>92818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,27 +1493,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1521,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696201</v>
+        <v>696098</v>
       </c>
       <c r="R9" t="n">
-        <v>6652094</v>
+        <v>6652123</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1584,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128402771</v>
+        <v>128403010</v>
       </c>
       <c r="B10" t="n">
-        <v>92818</v>
+        <v>101712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,26 +1594,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696098</v>
+        <v>696201</v>
       </c>
       <c r="R10" t="n">
-        <v>6652123</v>
+        <v>6652094</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
         <v>128403964</v>
       </c>
       <c r="B4" t="n">
-        <v>98641</v>
+        <v>98654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,43 +1049,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403713</v>
+        <v>128403486</v>
       </c>
       <c r="B5" t="n">
-        <v>4779</v>
+        <v>96878</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1093,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695845</v>
+        <v>696113</v>
       </c>
       <c r="R5" t="n">
-        <v>6652166</v>
+        <v>6652331</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,7 +1128,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal gran.</t>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,38 +1156,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403486</v>
+        <v>128403713</v>
       </c>
       <c r="B6" t="n">
-        <v>96865</v>
+        <v>4779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696113</v>
+        <v>695845</v>
       </c>
       <c r="R6" t="n">
-        <v>6652331</v>
+        <v>6652166</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tallåga.</t>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1378,7 +1378,7 @@
         <v>128403368</v>
       </c>
       <c r="B8" t="n">
-        <v>106244</v>
+        <v>106257</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>128402771</v>
       </c>
       <c r="B9" t="n">
-        <v>92818</v>
+        <v>92830</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>128403010</v>
       </c>
       <c r="B10" t="n">
-        <v>101712</v>
+        <v>101725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128403071</v>
       </c>
       <c r="B12" t="n">
-        <v>92191</v>
+        <v>92201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128403904</v>
+        <v>128403215</v>
       </c>
       <c r="B14" t="n">
-        <v>92429</v>
+        <v>91914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695775</v>
+        <v>696215</v>
       </c>
       <c r="R14" t="n">
-        <v>6652197</v>
+        <v>6652120</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2079,6 +2079,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På klen granlåga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,10 +2111,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128403215</v>
+        <v>128403904</v>
       </c>
       <c r="B15" t="n">
-        <v>91904</v>
+        <v>92439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,21 +2122,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4217</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2144,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696215</v>
+        <v>695775</v>
       </c>
       <c r="R15" t="n">
-        <v>6652120</v>
+        <v>6652197</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2182,11 +2187,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På klen granlåga.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
         <v>128403356</v>
       </c>
       <c r="B16" t="n">
-        <v>104087</v>
+        <v>104100</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>128403960</v>
       </c>
       <c r="B17" t="n">
-        <v>92802</v>
+        <v>92812</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128403876</v>
       </c>
       <c r="B18" t="n">
-        <v>96865</v>
+        <v>96878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2749,7 +2749,7 @@
         <v>128402802</v>
       </c>
       <c r="B21" t="n">
-        <v>92800</v>
+        <v>92810</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>128403286</v>
       </c>
       <c r="B22" t="n">
-        <v>100807</v>
+        <v>100820</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2965,7 +2965,7 @@
         <v>128402554</v>
       </c>
       <c r="B23" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>128403380</v>
       </c>
       <c r="B24" t="n">
-        <v>96865</v>
+        <v>96878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128402821</v>
       </c>
       <c r="B25" t="n">
-        <v>92818</v>
+        <v>92830</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128403975</v>
+        <v>128403359</v>
       </c>
       <c r="B26" t="n">
-        <v>100807</v>
+        <v>101725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,21 +3287,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695772</v>
+        <v>696248</v>
       </c>
       <c r="R26" t="n">
-        <v>6652213</v>
+        <v>6652101</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3378,10 +3378,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128403359</v>
+        <v>128403975</v>
       </c>
       <c r="B27" t="n">
-        <v>101712</v>
+        <v>100820</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696248</v>
+        <v>695772</v>
       </c>
       <c r="R27" t="n">
-        <v>6652101</v>
+        <v>6652213</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3483,7 +3483,7 @@
         <v>128402868</v>
       </c>
       <c r="B28" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>128403599</v>
       </c>
       <c r="B29" t="n">
-        <v>92820</v>
+        <v>92832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128403071</v>
+        <v>128403246</v>
       </c>
       <c r="B12" t="n">
-        <v>92201</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,26 +1803,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1830,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696228</v>
+        <v>696215</v>
       </c>
       <c r="R12" t="n">
-        <v>6652121</v>
+        <v>6652120</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1868,11 +1874,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På stubbe till grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1891,17 +1892,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128403246</v>
+        <v>128403071</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>92201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,32 +1910,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1942,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696215</v>
+        <v>696228</v>
       </c>
       <c r="R13" t="n">
-        <v>6652120</v>
+        <v>6652121</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1978,6 +1973,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På stubbe till grov granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128403359</v>
+        <v>128403975</v>
       </c>
       <c r="B26" t="n">
-        <v>101725</v>
+        <v>100820</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,21 +3287,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696248</v>
+        <v>695772</v>
       </c>
       <c r="R26" t="n">
-        <v>6652101</v>
+        <v>6652213</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3378,10 +3378,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128403975</v>
+        <v>128403359</v>
       </c>
       <c r="B27" t="n">
-        <v>100820</v>
+        <v>101725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695772</v>
+        <v>696248</v>
       </c>
       <c r="R27" t="n">
-        <v>6652213</v>
+        <v>6652101</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -2746,45 +2746,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128402802</v>
+        <v>128403286</v>
       </c>
       <c r="B21" t="n">
-        <v>92810</v>
+        <v>100820</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2792,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696097</v>
+        <v>696215</v>
       </c>
       <c r="R21" t="n">
-        <v>6652131</v>
+        <v>6652120</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2830,6 +2823,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spritt inom biotopen.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2848,45 +2846,52 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128403286</v>
+        <v>128402802</v>
       </c>
       <c r="B22" t="n">
-        <v>100820</v>
+        <v>92810</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2894,10 +2899,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696215</v>
+        <v>696097</v>
       </c>
       <c r="R22" t="n">
-        <v>6652120</v>
+        <v>6652131</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2932,11 +2937,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spritt inom biotopen.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -1049,38 +1049,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403486</v>
+        <v>128403713</v>
       </c>
       <c r="B5" t="n">
-        <v>96878</v>
+        <v>4779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696113</v>
+        <v>695845</v>
       </c>
       <c r="R5" t="n">
-        <v>6652331</v>
+        <v>6652166</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,7 +1133,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tallåga.</t>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,43 +1161,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403713</v>
+        <v>128403368</v>
       </c>
       <c r="B6" t="n">
-        <v>4779</v>
+        <v>106257</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695845</v>
+        <v>696248</v>
       </c>
       <c r="R6" t="n">
-        <v>6652166</v>
+        <v>6652101</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal gran.</t>
+          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1375,32 +1375,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128403368</v>
+        <v>128403486</v>
       </c>
       <c r="B8" t="n">
-        <v>106257</v>
+        <v>96878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696248</v>
+        <v>696113</v>
       </c>
       <c r="R8" t="n">
-        <v>6652101</v>
+        <v>6652331</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka självföryngrad ung ask.</t>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128403215</v>
+        <v>128403904</v>
       </c>
       <c r="B14" t="n">
-        <v>91914</v>
+        <v>92439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4217</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696215</v>
+        <v>695775</v>
       </c>
       <c r="R14" t="n">
-        <v>6652120</v>
+        <v>6652197</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,11 +2081,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På klen granlåga.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2104,17 +2099,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128403904</v>
+        <v>128403215</v>
       </c>
       <c r="B15" t="n">
-        <v>92439</v>
+        <v>91914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,21 +2117,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2144,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695775</v>
+        <v>696215</v>
       </c>
       <c r="R15" t="n">
-        <v>6652197</v>
+        <v>6652120</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2185,6 +2180,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På klen granlåga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2746,38 +2746,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128403286</v>
+        <v>128402802</v>
       </c>
       <c r="B21" t="n">
-        <v>100820</v>
+        <v>92810</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2785,10 +2792,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696215</v>
+        <v>696097</v>
       </c>
       <c r="R21" t="n">
-        <v>6652120</v>
+        <v>6652131</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2823,11 +2830,6 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spritt inom biotopen.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2846,52 +2848,45 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128402802</v>
+        <v>128403286</v>
       </c>
       <c r="B22" t="n">
-        <v>92810</v>
+        <v>100820</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2899,10 +2894,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696097</v>
+        <v>696215</v>
       </c>
       <c r="R22" t="n">
-        <v>6652131</v>
+        <v>6652120</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2935,6 +2930,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spritt inom biotopen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128403975</v>
+        <v>128403359</v>
       </c>
       <c r="B26" t="n">
-        <v>100820</v>
+        <v>101725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,21 +3287,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695772</v>
+        <v>696248</v>
       </c>
       <c r="R26" t="n">
-        <v>6652213</v>
+        <v>6652101</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3378,10 +3378,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128403359</v>
+        <v>128403975</v>
       </c>
       <c r="B27" t="n">
-        <v>101725</v>
+        <v>100820</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696248</v>
+        <v>695772</v>
       </c>
       <c r="R27" t="n">
-        <v>6652101</v>
+        <v>6652213</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128402868</v>
+        <v>128403599</v>
       </c>
       <c r="B28" t="n">
-        <v>91522</v>
+        <v>92832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,25 +3491,33 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3518,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696147</v>
+        <v>696018</v>
       </c>
       <c r="R28" t="n">
-        <v>6652092</v>
+        <v>6652291</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3554,11 +3562,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gren av torrgran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3586,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128403599</v>
+        <v>128402868</v>
       </c>
       <c r="B29" t="n">
-        <v>92832</v>
+        <v>91522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3597,33 +3600,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3632,10 +3627,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696018</v>
+        <v>696147</v>
       </c>
       <c r="R29" t="n">
-        <v>6652291</v>
+        <v>6652092</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3668,6 +3663,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gren av torrgran.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
         <v>128403964</v>
       </c>
       <c r="B4" t="n">
-        <v>98654</v>
+        <v>98658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,43 +1049,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403713</v>
+        <v>128403486</v>
       </c>
       <c r="B5" t="n">
-        <v>4779</v>
+        <v>96882</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1093,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695845</v>
+        <v>696113</v>
       </c>
       <c r="R5" t="n">
-        <v>6652166</v>
+        <v>6652331</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,7 +1128,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal gran.</t>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,38 +1156,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403368</v>
+        <v>128403713</v>
       </c>
       <c r="B6" t="n">
-        <v>106257</v>
+        <v>4779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696248</v>
+        <v>695845</v>
       </c>
       <c r="R6" t="n">
-        <v>6652101</v>
+        <v>6652166</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka självföryngrad ung ask.</t>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,43 +1268,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128403732</v>
+        <v>128403368</v>
       </c>
       <c r="B7" t="n">
-        <v>5197</v>
+        <v>106261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695846</v>
+        <v>696248</v>
       </c>
       <c r="R7" t="n">
-        <v>6652175</v>
+        <v>6652101</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,6 +1343,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,38 +1375,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128403486</v>
+        <v>128403732</v>
       </c>
       <c r="B8" t="n">
-        <v>96878</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696113</v>
+        <v>695846</v>
       </c>
       <c r="R8" t="n">
-        <v>6652331</v>
+        <v>6652175</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,11 +1455,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,7 +1485,7 @@
         <v>128402771</v>
       </c>
       <c r="B9" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>128403010</v>
       </c>
       <c r="B10" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128403246</v>
+        <v>128403071</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>92205</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,32 +1803,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1836,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696215</v>
+        <v>696228</v>
       </c>
       <c r="R12" t="n">
-        <v>6652120</v>
+        <v>6652121</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1872,6 +1866,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På stubbe till grov granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128403071</v>
+        <v>128403246</v>
       </c>
       <c r="B13" t="n">
-        <v>92201</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,26 +1909,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1937,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696228</v>
+        <v>696215</v>
       </c>
       <c r="R13" t="n">
-        <v>6652121</v>
+        <v>6652120</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1973,11 +1978,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På stubbe till grov granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128403904</v>
+        <v>128403215</v>
       </c>
       <c r="B14" t="n">
-        <v>92439</v>
+        <v>91918</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>695775</v>
+        <v>696215</v>
       </c>
       <c r="R14" t="n">
-        <v>6652197</v>
+        <v>6652120</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2079,6 +2079,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På klen granlåga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,10 +2111,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128403215</v>
+        <v>128403904</v>
       </c>
       <c r="B15" t="n">
-        <v>91914</v>
+        <v>92443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,21 +2122,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4217</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2144,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696215</v>
+        <v>695775</v>
       </c>
       <c r="R15" t="n">
-        <v>6652120</v>
+        <v>6652197</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2180,11 +2185,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På klen granlåga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,7 +2215,7 @@
         <v>128403356</v>
       </c>
       <c r="B16" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>128403960</v>
       </c>
       <c r="B17" t="n">
-        <v>92812</v>
+        <v>92816</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128403876</v>
       </c>
       <c r="B18" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>128402802</v>
       </c>
       <c r="B21" t="n">
-        <v>92810</v>
+        <v>92814</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>128403286</v>
       </c>
       <c r="B22" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>128402554</v>
       </c>
       <c r="B23" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3071,7 +3071,7 @@
         <v>128403380</v>
       </c>
       <c r="B24" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128402821</v>
       </c>
       <c r="B25" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128403359</v>
+        <v>128403975</v>
       </c>
       <c r="B26" t="n">
-        <v>101725</v>
+        <v>100824</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,21 +3287,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696248</v>
+        <v>695772</v>
       </c>
       <c r="R26" t="n">
-        <v>6652101</v>
+        <v>6652213</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3378,10 +3378,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128403975</v>
+        <v>128403359</v>
       </c>
       <c r="B27" t="n">
-        <v>100820</v>
+        <v>101729</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695772</v>
+        <v>696248</v>
       </c>
       <c r="R27" t="n">
-        <v>6652213</v>
+        <v>6652101</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3483,7 +3483,7 @@
         <v>128403599</v>
       </c>
       <c r="B28" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>128402868</v>
       </c>
       <c r="B29" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128402771</v>
+        <v>128403010</v>
       </c>
       <c r="B9" t="n">
-        <v>92834</v>
+        <v>101729</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,26 +1493,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1520,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696098</v>
+        <v>696201</v>
       </c>
       <c r="R9" t="n">
-        <v>6652123</v>
+        <v>6652094</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1583,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128403010</v>
+        <v>128402771</v>
       </c>
       <c r="B10" t="n">
-        <v>101729</v>
+        <v>92834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,27 +1595,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696201</v>
+        <v>696098</v>
       </c>
       <c r="R10" t="n">
-        <v>6652094</v>
+        <v>6652123</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128403975</v>
+        <v>128403359</v>
       </c>
       <c r="B26" t="n">
-        <v>100824</v>
+        <v>101729</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,21 +3287,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>695772</v>
+        <v>696248</v>
       </c>
       <c r="R26" t="n">
-        <v>6652213</v>
+        <v>6652101</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3378,10 +3378,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128403359</v>
+        <v>128403975</v>
       </c>
       <c r="B27" t="n">
-        <v>101729</v>
+        <v>100824</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696248</v>
+        <v>695772</v>
       </c>
       <c r="R27" t="n">
-        <v>6652101</v>
+        <v>6652213</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
         <v>128403964</v>
       </c>
       <c r="B4" t="n">
-        <v>98658</v>
+        <v>98665</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,38 +1049,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128403486</v>
+        <v>128403713</v>
       </c>
       <c r="B5" t="n">
-        <v>96882</v>
+        <v>4779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696113</v>
+        <v>695845</v>
       </c>
       <c r="R5" t="n">
-        <v>6652331</v>
+        <v>6652166</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,7 +1133,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tallåga.</t>
+          <t>Gnagspår i barken på gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,43 +1161,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128403713</v>
+        <v>128403486</v>
       </c>
       <c r="B6" t="n">
-        <v>4779</v>
+        <v>96889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695845</v>
+        <v>696113</v>
       </c>
       <c r="R6" t="n">
-        <v>6652166</v>
+        <v>6652331</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gnagspår i barken på gammal gran.</t>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,38 +1268,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128403368</v>
+        <v>128403732</v>
       </c>
       <c r="B7" t="n">
-        <v>106261</v>
+        <v>5197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696248</v>
+        <v>695846</v>
       </c>
       <c r="R7" t="n">
-        <v>6652101</v>
+        <v>6652175</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,11 +1348,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,43 +1375,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128403732</v>
+        <v>128403368</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>106268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1419,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695846</v>
+        <v>696248</v>
       </c>
       <c r="R8" t="n">
-        <v>6652175</v>
+        <v>6652101</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,6 +1450,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka självföryngrad ung ask.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128403010</v>
+        <v>128402771</v>
       </c>
       <c r="B9" t="n">
-        <v>101729</v>
+        <v>92839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,27 +1493,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1521,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696201</v>
+        <v>696098</v>
       </c>
       <c r="R9" t="n">
-        <v>6652094</v>
+        <v>6652123</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1584,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128402771</v>
+        <v>128403010</v>
       </c>
       <c r="B10" t="n">
-        <v>92834</v>
+        <v>101736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,26 +1594,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696098</v>
+        <v>696201</v>
       </c>
       <c r="R10" t="n">
-        <v>6652123</v>
+        <v>6652094</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1795,7 +1795,7 @@
         <v>128403071</v>
       </c>
       <c r="B12" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128403215</v>
+        <v>128403904</v>
       </c>
       <c r="B14" t="n">
-        <v>91918</v>
+        <v>92448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4217</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696215</v>
+        <v>695775</v>
       </c>
       <c r="R14" t="n">
-        <v>6652120</v>
+        <v>6652197</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2079,11 +2079,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På klen granlåga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128403904</v>
+        <v>128403215</v>
       </c>
       <c r="B15" t="n">
-        <v>92443</v>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,21 +2117,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2144,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>695775</v>
+        <v>696215</v>
       </c>
       <c r="R15" t="n">
-        <v>6652197</v>
+        <v>6652120</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2187,6 +2182,11 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På klen granlåga.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
         <v>128403356</v>
       </c>
       <c r="B16" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>128403960</v>
       </c>
       <c r="B17" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128403876</v>
       </c>
       <c r="B18" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>128402802</v>
       </c>
       <c r="B21" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>128403286</v>
       </c>
       <c r="B22" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
+          <t>Kjell Håkan  Andersson , Bo Törnquist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2965,7 +2965,7 @@
         <v>128402554</v>
       </c>
       <c r="B23" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>128403380</v>
       </c>
       <c r="B24" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128402821</v>
       </c>
       <c r="B25" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128403359</v>
+        <v>128403975</v>
       </c>
       <c r="B26" t="n">
-        <v>101729</v>
+        <v>100831</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,21 +3287,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696248</v>
+        <v>695772</v>
       </c>
       <c r="R26" t="n">
-        <v>6652101</v>
+        <v>6652213</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3378,10 +3378,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128403975</v>
+        <v>128403359</v>
       </c>
       <c r="B27" t="n">
-        <v>100824</v>
+        <v>101736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695772</v>
+        <v>696248</v>
       </c>
       <c r="R27" t="n">
-        <v>6652213</v>
+        <v>6652101</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128403599</v>
+        <v>128402868</v>
       </c>
       <c r="B28" t="n">
-        <v>92836</v>
+        <v>91531</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,33 +3491,25 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3526,10 +3518,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696018</v>
+        <v>696147</v>
       </c>
       <c r="R28" t="n">
-        <v>6652291</v>
+        <v>6652092</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3562,6 +3554,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gren av torrgran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3586,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128402868</v>
+        <v>128403599</v>
       </c>
       <c r="B29" t="n">
-        <v>91526</v>
+        <v>92841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,25 +3597,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3627,10 +3632,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696147</v>
+        <v>696018</v>
       </c>
       <c r="R29" t="n">
-        <v>6652092</v>
+        <v>6652291</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3663,11 +3668,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gren av torrgran.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3986,47 +3986,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129094741</v>
+        <v>129095299</v>
       </c>
       <c r="B33" t="n">
-        <v>87041</v>
+        <v>91975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3624</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696155</v>
+        <v>696057</v>
       </c>
       <c r="R33" t="n">
-        <v>6652354</v>
+        <v>6652483</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4064,7 +4065,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4083,48 +4083,47 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129095299</v>
+        <v>129094741</v>
       </c>
       <c r="B34" t="n">
-        <v>91975</v>
+        <v>87041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>3624</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696057</v>
+        <v>696155</v>
       </c>
       <c r="R34" t="n">
-        <v>6652483</v>
+        <v>6652354</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4162,6 +4161,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129095794</v>
+        <v>129096138</v>
       </c>
       <c r="B38" t="n">
-        <v>92849</v>
+        <v>91538</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4487,21 +4487,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695984</v>
+        <v>695953</v>
       </c>
       <c r="R38" t="n">
-        <v>6652567</v>
+        <v>6652663</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,10 +4573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129096138</v>
+        <v>129095794</v>
       </c>
       <c r="B39" t="n">
-        <v>91538</v>
+        <v>92849</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4584,21 +4584,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695953</v>
+        <v>695984</v>
       </c>
       <c r="R39" t="n">
-        <v>6652663</v>
+        <v>6652567</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5437,10 +5437,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129096108</v>
+        <v>129096633</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>100745</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5448,21 +5448,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>222771</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>695953</v>
+        <v>696078</v>
       </c>
       <c r="R48" t="n">
-        <v>6652663</v>
+        <v>6652601</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129097950</v>
+        <v>129096360</v>
       </c>
       <c r="B49" t="n">
-        <v>92456</v>
+        <v>100839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,13 +5569,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696312</v>
+        <v>696042</v>
       </c>
       <c r="R49" t="n">
-        <v>6652356</v>
+        <v>6652606</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5631,32 +5631,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129097529</v>
+        <v>129097950</v>
       </c>
       <c r="B50" t="n">
-        <v>91520</v>
+        <v>92456</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696166</v>
+        <v>696312</v>
       </c>
       <c r="R50" t="n">
-        <v>6652538</v>
+        <v>6652356</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,32 +5728,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129096633</v>
+        <v>129097529</v>
       </c>
       <c r="B51" t="n">
-        <v>100745</v>
+        <v>91520</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,10 +5763,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696078</v>
+        <v>696166</v>
       </c>
       <c r="R51" t="n">
-        <v>6652601</v>
+        <v>6652538</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129096360</v>
+        <v>129096108</v>
       </c>
       <c r="B52" t="n">
-        <v>100839</v>
+        <v>5177</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,21 +5836,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5860,13 +5860,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696042</v>
+        <v>695953</v>
       </c>
       <c r="R52" t="n">
-        <v>6652606</v>
+        <v>6652663</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3698,7 +3698,7 @@
         <v>129095316</v>
       </c>
       <c r="B30" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>129096111</v>
       </c>
       <c r="B31" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129096950</v>
       </c>
       <c r="B32" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>129095299</v>
       </c>
       <c r="B33" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>129094741</v>
       </c>
       <c r="B34" t="n">
-        <v>87041</v>
+        <v>87044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>91732</v>
+        <v>91735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>105799</v>
+        <v>105804</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>101744</v>
+        <v>101749</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>129096138</v>
       </c>
       <c r="B38" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>129095794</v>
       </c>
       <c r="B39" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>129095746</v>
       </c>
       <c r="B40" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>129096063</v>
       </c>
       <c r="B41" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>129095080</v>
       </c>
       <c r="B42" t="n">
-        <v>87041</v>
+        <v>87044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>129097843</v>
       </c>
       <c r="B43" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>129097563</v>
       </c>
       <c r="B44" t="n">
-        <v>91732</v>
+        <v>91735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>129096022</v>
       </c>
       <c r="B45" t="n">
-        <v>91928</v>
+        <v>91931</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>129096736</v>
       </c>
       <c r="B46" t="n">
-        <v>95980</v>
+        <v>95985</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>129097597</v>
       </c>
       <c r="B47" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5437,10 +5437,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129096633</v>
+        <v>129097950</v>
       </c>
       <c r="B48" t="n">
-        <v>100745</v>
+        <v>92461</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5448,21 +5448,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696078</v>
+        <v>696312</v>
       </c>
       <c r="R48" t="n">
-        <v>6652601</v>
+        <v>6652356</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129096360</v>
+        <v>129096633</v>
       </c>
       <c r="B49" t="n">
-        <v>100839</v>
+        <v>100750</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,13 +5569,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696042</v>
+        <v>696078</v>
       </c>
       <c r="R49" t="n">
-        <v>6652606</v>
+        <v>6652601</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129097950</v>
+        <v>129096360</v>
       </c>
       <c r="B50" t="n">
-        <v>92456</v>
+        <v>100844</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,13 +5666,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696312</v>
+        <v>696042</v>
       </c>
       <c r="R50" t="n">
-        <v>6652356</v>
+        <v>6652606</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>129097529</v>
       </c>
       <c r="B51" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>129097801</v>
       </c>
       <c r="B53" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>129097202</v>
       </c>
       <c r="B54" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3698,7 +3698,7 @@
         <v>129095316</v>
       </c>
       <c r="B30" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>129096111</v>
       </c>
       <c r="B31" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129096950</v>
       </c>
       <c r="B32" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>129095299</v>
       </c>
       <c r="B33" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>129094741</v>
       </c>
       <c r="B34" t="n">
-        <v>87044</v>
+        <v>87047</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>91735</v>
+        <v>91738</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>105804</v>
+        <v>105807</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>101749</v>
+        <v>101752</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>129096138</v>
       </c>
       <c r="B38" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>129095794</v>
       </c>
       <c r="B39" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>129095746</v>
       </c>
       <c r="B40" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>129096063</v>
       </c>
       <c r="B41" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>129095080</v>
       </c>
       <c r="B42" t="n">
-        <v>87044</v>
+        <v>87047</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>129097843</v>
       </c>
       <c r="B43" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>129097563</v>
       </c>
       <c r="B44" t="n">
-        <v>91735</v>
+        <v>91738</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>129096022</v>
       </c>
       <c r="B45" t="n">
-        <v>91931</v>
+        <v>91934</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>129096736</v>
       </c>
       <c r="B46" t="n">
-        <v>95985</v>
+        <v>95988</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>129097597</v>
       </c>
       <c r="B47" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5437,32 +5437,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129097950</v>
+        <v>129097529</v>
       </c>
       <c r="B48" t="n">
-        <v>92461</v>
+        <v>91526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696312</v>
+        <v>696166</v>
       </c>
       <c r="R48" t="n">
-        <v>6652356</v>
+        <v>6652538</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129096633</v>
+        <v>129097950</v>
       </c>
       <c r="B49" t="n">
-        <v>100750</v>
+        <v>92464</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696078</v>
+        <v>696312</v>
       </c>
       <c r="R49" t="n">
-        <v>6652601</v>
+        <v>6652356</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129096360</v>
+        <v>129096633</v>
       </c>
       <c r="B50" t="n">
-        <v>100844</v>
+        <v>100753</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,13 +5666,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696042</v>
+        <v>696078</v>
       </c>
       <c r="R50" t="n">
-        <v>6652606</v>
+        <v>6652601</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5728,32 +5728,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129097529</v>
+        <v>129096360</v>
       </c>
       <c r="B51" t="n">
-        <v>91523</v>
+        <v>100847</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,13 +5763,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696166</v>
+        <v>696042</v>
       </c>
       <c r="R51" t="n">
-        <v>6652538</v>
+        <v>6652606</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>129097801</v>
       </c>
       <c r="B53" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>129097202</v>
       </c>
       <c r="B54" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -4180,32 +4180,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129097381</v>
+        <v>129097762</v>
       </c>
       <c r="B35" t="n">
-        <v>91738</v>
+        <v>101752</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1106</v>
+        <v>221235</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4215,13 +4215,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696125</v>
+        <v>696154</v>
       </c>
       <c r="R35" t="n">
-        <v>6652488</v>
+        <v>6652433</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4251,11 +4251,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4282,32 +4277,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096372</v>
+        <v>129097381</v>
       </c>
       <c r="B36" t="n">
-        <v>105807</v>
+        <v>91738</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221423</v>
+        <v>1106</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4317,10 +4312,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696042</v>
+        <v>696125</v>
       </c>
       <c r="R36" t="n">
-        <v>6652606</v>
+        <v>6652488</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4353,6 +4348,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4379,10 +4379,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129097762</v>
+        <v>129096372</v>
       </c>
       <c r="B37" t="n">
-        <v>101752</v>
+        <v>105807</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221235</v>
+        <v>221423</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4414,13 +4414,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696154</v>
+        <v>696042</v>
       </c>
       <c r="R37" t="n">
-        <v>6652433</v>
+        <v>6652606</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096138</v>
+        <v>129095794</v>
       </c>
       <c r="B38" t="n">
-        <v>91544</v>
+        <v>92857</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4487,21 +4487,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695953</v>
+        <v>695984</v>
       </c>
       <c r="R38" t="n">
-        <v>6652663</v>
+        <v>6652567</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,10 +4573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129095794</v>
+        <v>129096138</v>
       </c>
       <c r="B39" t="n">
-        <v>92857</v>
+        <v>91544</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4584,21 +4584,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695984</v>
+        <v>695953</v>
       </c>
       <c r="R39" t="n">
-        <v>6652567</v>
+        <v>6652663</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5437,32 +5437,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129097529</v>
+        <v>129096633</v>
       </c>
       <c r="B48" t="n">
-        <v>91526</v>
+        <v>100753</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696166</v>
+        <v>696078</v>
       </c>
       <c r="R48" t="n">
-        <v>6652538</v>
+        <v>6652601</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129097950</v>
+        <v>129096360</v>
       </c>
       <c r="B49" t="n">
-        <v>92464</v>
+        <v>100847</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,13 +5569,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696312</v>
+        <v>696042</v>
       </c>
       <c r="R49" t="n">
-        <v>6652356</v>
+        <v>6652606</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5631,32 +5631,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129096633</v>
+        <v>129097529</v>
       </c>
       <c r="B50" t="n">
-        <v>100753</v>
+        <v>91526</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696078</v>
+        <v>696166</v>
       </c>
       <c r="R50" t="n">
-        <v>6652601</v>
+        <v>6652538</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129096360</v>
+        <v>129097950</v>
       </c>
       <c r="B51" t="n">
-        <v>100847</v>
+        <v>92464</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,13 +5763,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696042</v>
+        <v>696312</v>
       </c>
       <c r="R51" t="n">
-        <v>6652606</v>
+        <v>6652356</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -4180,32 +4180,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129097762</v>
+        <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>101752</v>
+        <v>91738</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221235</v>
+        <v>1106</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4215,13 +4215,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696154</v>
+        <v>696125</v>
       </c>
       <c r="R35" t="n">
-        <v>6652433</v>
+        <v>6652488</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4251,6 +4251,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4277,32 +4282,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129097381</v>
+        <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>91738</v>
+        <v>105807</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1106</v>
+        <v>221423</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4312,10 +4317,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696125</v>
+        <v>696042</v>
       </c>
       <c r="R36" t="n">
-        <v>6652488</v>
+        <v>6652606</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4348,11 +4353,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4379,10 +4379,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096372</v>
+        <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>105807</v>
+        <v>101752</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4414,13 +4414,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696042</v>
+        <v>696154</v>
       </c>
       <c r="R37" t="n">
-        <v>6652606</v>
+        <v>6652433</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5437,32 +5437,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129096633</v>
+        <v>129097529</v>
       </c>
       <c r="B48" t="n">
-        <v>100753</v>
+        <v>91526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696078</v>
+        <v>696166</v>
       </c>
       <c r="R48" t="n">
-        <v>6652601</v>
+        <v>6652538</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129096360</v>
+        <v>129097950</v>
       </c>
       <c r="B49" t="n">
-        <v>100847</v>
+        <v>92464</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,13 +5569,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696042</v>
+        <v>696312</v>
       </c>
       <c r="R49" t="n">
-        <v>6652606</v>
+        <v>6652356</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5631,32 +5631,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129097529</v>
+        <v>129096633</v>
       </c>
       <c r="B50" t="n">
-        <v>91526</v>
+        <v>100753</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696166</v>
+        <v>696078</v>
       </c>
       <c r="R50" t="n">
-        <v>6652538</v>
+        <v>6652601</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129097950</v>
+        <v>129096360</v>
       </c>
       <c r="B51" t="n">
-        <v>92464</v>
+        <v>100847</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,13 +5763,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696312</v>
+        <v>696042</v>
       </c>
       <c r="R51" t="n">
-        <v>6652356</v>
+        <v>6652606</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3986,48 +3986,47 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129095299</v>
+        <v>129094741</v>
       </c>
       <c r="B33" t="n">
-        <v>91981</v>
+        <v>87047</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>3624</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696057</v>
+        <v>696155</v>
       </c>
       <c r="R33" t="n">
-        <v>6652483</v>
+        <v>6652354</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4065,6 +4064,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4083,47 +4083,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129094741</v>
+        <v>129095299</v>
       </c>
       <c r="B34" t="n">
-        <v>87047</v>
+        <v>91981</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3624</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696155</v>
+        <v>696057</v>
       </c>
       <c r="R34" t="n">
-        <v>6652354</v>
+        <v>6652483</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4161,7 +4162,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4180,32 +4180,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129097381</v>
+        <v>129096372</v>
       </c>
       <c r="B35" t="n">
-        <v>91738</v>
+        <v>105807</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1106</v>
+        <v>221423</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696125</v>
+        <v>696042</v>
       </c>
       <c r="R35" t="n">
-        <v>6652488</v>
+        <v>6652606</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4251,11 +4251,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4282,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096372</v>
+        <v>129097762</v>
       </c>
       <c r="B36" t="n">
-        <v>105807</v>
+        <v>101752</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4293,21 +4288,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4317,13 +4312,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696042</v>
+        <v>696154</v>
       </c>
       <c r="R36" t="n">
-        <v>6652606</v>
+        <v>6652433</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4379,32 +4374,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129097762</v>
+        <v>129097381</v>
       </c>
       <c r="B37" t="n">
-        <v>101752</v>
+        <v>91738</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221235</v>
+        <v>1106</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4414,13 +4409,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696154</v>
+        <v>696125</v>
       </c>
       <c r="R37" t="n">
-        <v>6652433</v>
+        <v>6652488</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4450,6 +4445,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129095794</v>
+        <v>129096138</v>
       </c>
       <c r="B38" t="n">
-        <v>92857</v>
+        <v>91544</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4487,21 +4487,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695984</v>
+        <v>695953</v>
       </c>
       <c r="R38" t="n">
-        <v>6652567</v>
+        <v>6652663</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,10 +4573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129096138</v>
+        <v>129095794</v>
       </c>
       <c r="B39" t="n">
-        <v>91544</v>
+        <v>92857</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4584,21 +4584,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695953</v>
+        <v>695984</v>
       </c>
       <c r="R39" t="n">
-        <v>6652663</v>
+        <v>6652567</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5437,32 +5437,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129097529</v>
+        <v>129096108</v>
       </c>
       <c r="B48" t="n">
-        <v>91526</v>
+        <v>5177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696166</v>
+        <v>695953</v>
       </c>
       <c r="R48" t="n">
-        <v>6652538</v>
+        <v>6652663</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,32 +5534,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129097950</v>
+        <v>129097529</v>
       </c>
       <c r="B49" t="n">
-        <v>92464</v>
+        <v>91526</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696312</v>
+        <v>696166</v>
       </c>
       <c r="R49" t="n">
-        <v>6652356</v>
+        <v>6652538</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129096633</v>
+        <v>129097950</v>
       </c>
       <c r="B50" t="n">
-        <v>100753</v>
+        <v>92464</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696078</v>
+        <v>696312</v>
       </c>
       <c r="R50" t="n">
-        <v>6652601</v>
+        <v>6652356</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5825,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129096108</v>
+        <v>129096633</v>
       </c>
       <c r="B52" t="n">
-        <v>5177</v>
+        <v>100753</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,21 +5836,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>222771</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>695953</v>
+        <v>696078</v>
       </c>
       <c r="R52" t="n">
-        <v>6652663</v>
+        <v>6652601</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3698,7 +3698,7 @@
         <v>129095316</v>
       </c>
       <c r="B30" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>129096111</v>
       </c>
       <c r="B31" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129096950</v>
       </c>
       <c r="B32" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3986,47 +3986,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129094741</v>
+        <v>129095299</v>
       </c>
       <c r="B33" t="n">
-        <v>87047</v>
+        <v>91988</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3624</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696155</v>
+        <v>696057</v>
       </c>
       <c r="R33" t="n">
-        <v>6652354</v>
+        <v>6652483</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4064,7 +4065,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4083,48 +4083,47 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129095299</v>
+        <v>129094741</v>
       </c>
       <c r="B34" t="n">
-        <v>91981</v>
+        <v>87051</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>3624</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696057</v>
+        <v>696155</v>
       </c>
       <c r="R34" t="n">
-        <v>6652483</v>
+        <v>6652354</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4162,6 +4161,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4180,32 +4180,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129096372</v>
+        <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>105807</v>
+        <v>91745</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221423</v>
+        <v>1106</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696042</v>
+        <v>696125</v>
       </c>
       <c r="R35" t="n">
-        <v>6652606</v>
+        <v>6652488</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4251,6 +4251,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4277,10 +4282,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129097762</v>
+        <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>101752</v>
+        <v>105817</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,21 +4293,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221235</v>
+        <v>221423</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4312,13 +4317,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696154</v>
+        <v>696042</v>
       </c>
       <c r="R36" t="n">
-        <v>6652433</v>
+        <v>6652606</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4374,32 +4379,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129097381</v>
+        <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>91738</v>
+        <v>101762</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1106</v>
+        <v>221235</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4409,13 +4414,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696125</v>
+        <v>696154</v>
       </c>
       <c r="R37" t="n">
-        <v>6652488</v>
+        <v>6652433</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4445,11 +4450,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4479,7 +4479,7 @@
         <v>129096138</v>
       </c>
       <c r="B38" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>129095794</v>
       </c>
       <c r="B39" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>129095746</v>
       </c>
       <c r="B40" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>129096063</v>
       </c>
       <c r="B41" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>129095080</v>
       </c>
       <c r="B42" t="n">
-        <v>87047</v>
+        <v>87051</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>129097843</v>
       </c>
       <c r="B43" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>129097563</v>
       </c>
       <c r="B44" t="n">
-        <v>91738</v>
+        <v>91745</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>129096022</v>
       </c>
       <c r="B45" t="n">
-        <v>91934</v>
+        <v>91941</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>129096736</v>
       </c>
       <c r="B46" t="n">
-        <v>95988</v>
+        <v>95998</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>129097597</v>
       </c>
       <c r="B47" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5437,32 +5437,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129096108</v>
+        <v>129097529</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>91533</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>695953</v>
+        <v>696166</v>
       </c>
       <c r="R48" t="n">
-        <v>6652663</v>
+        <v>6652538</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,32 +5534,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129097529</v>
+        <v>129097950</v>
       </c>
       <c r="B49" t="n">
-        <v>91526</v>
+        <v>92471</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696166</v>
+        <v>696312</v>
       </c>
       <c r="R49" t="n">
-        <v>6652538</v>
+        <v>6652356</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129097950</v>
+        <v>129096108</v>
       </c>
       <c r="B50" t="n">
-        <v>92464</v>
+        <v>5177</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4769</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696312</v>
+        <v>695953</v>
       </c>
       <c r="R50" t="n">
-        <v>6652356</v>
+        <v>6652663</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129096360</v>
+        <v>129096633</v>
       </c>
       <c r="B51" t="n">
-        <v>100847</v>
+        <v>100763</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,13 +5763,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696042</v>
+        <v>696078</v>
       </c>
       <c r="R51" t="n">
-        <v>6652606</v>
+        <v>6652601</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5825,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129096633</v>
+        <v>129096360</v>
       </c>
       <c r="B52" t="n">
-        <v>100753</v>
+        <v>100857</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,21 +5836,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5860,13 +5860,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696078</v>
+        <v>696042</v>
       </c>
       <c r="R52" t="n">
-        <v>6652601</v>
+        <v>6652606</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>129097801</v>
       </c>
       <c r="B53" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>129097202</v>
       </c>
       <c r="B54" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096138</v>
+        <v>129095794</v>
       </c>
       <c r="B38" t="n">
-        <v>91551</v>
+        <v>92864</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4487,21 +4487,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695953</v>
+        <v>695984</v>
       </c>
       <c r="R38" t="n">
-        <v>6652663</v>
+        <v>6652567</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,10 +4573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129095794</v>
+        <v>129096138</v>
       </c>
       <c r="B39" t="n">
-        <v>92864</v>
+        <v>91551</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4584,21 +4584,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695984</v>
+        <v>695953</v>
       </c>
       <c r="R39" t="n">
-        <v>6652567</v>
+        <v>6652663</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3698,7 +3698,7 @@
         <v>129095316</v>
       </c>
       <c r="B30" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>129096111</v>
       </c>
       <c r="B31" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129096950</v>
       </c>
       <c r="B32" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>129095299</v>
       </c>
       <c r="B33" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>129094741</v>
       </c>
       <c r="B34" t="n">
-        <v>87051</v>
+        <v>87058</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>91745</v>
+        <v>91752</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>105817</v>
+        <v>105824</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>101762</v>
+        <v>101769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129095794</v>
+        <v>129096138</v>
       </c>
       <c r="B38" t="n">
-        <v>92864</v>
+        <v>91558</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4487,21 +4487,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695984</v>
+        <v>695953</v>
       </c>
       <c r="R38" t="n">
-        <v>6652567</v>
+        <v>6652663</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,10 +4573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129096138</v>
+        <v>129095794</v>
       </c>
       <c r="B39" t="n">
-        <v>91551</v>
+        <v>92871</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4584,21 +4584,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695953</v>
+        <v>695984</v>
       </c>
       <c r="R39" t="n">
-        <v>6652663</v>
+        <v>6652567</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4673,7 +4673,7 @@
         <v>129095746</v>
       </c>
       <c r="B40" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>129096063</v>
       </c>
       <c r="B41" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>129095080</v>
       </c>
       <c r="B42" t="n">
-        <v>87051</v>
+        <v>87058</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>129097843</v>
       </c>
       <c r="B43" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5054,32 +5054,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129097563</v>
+        <v>129096022</v>
       </c>
       <c r="B44" t="n">
-        <v>91745</v>
+        <v>91948</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1106</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Vågticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5089,10 +5084,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696166</v>
+        <v>695988</v>
       </c>
       <c r="R44" t="n">
-        <v>6652538</v>
+        <v>6652611</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5151,27 +5146,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129096022</v>
+        <v>129097563</v>
       </c>
       <c r="B45" t="n">
-        <v>91941</v>
+        <v>91752</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6040186</v>
+        <v>1106</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695988</v>
+        <v>696166</v>
       </c>
       <c r="R45" t="n">
-        <v>6652611</v>
+        <v>6652538</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5246,7 +5246,7 @@
         <v>129096736</v>
       </c>
       <c r="B46" t="n">
-        <v>95998</v>
+        <v>96005</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>129097597</v>
       </c>
       <c r="B47" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5437,32 +5437,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129097529</v>
+        <v>129097950</v>
       </c>
       <c r="B48" t="n">
-        <v>91533</v>
+        <v>92478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696166</v>
+        <v>696312</v>
       </c>
       <c r="R48" t="n">
-        <v>6652538</v>
+        <v>6652356</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129097950</v>
+        <v>129096108</v>
       </c>
       <c r="B49" t="n">
-        <v>92471</v>
+        <v>5177</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4769</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696312</v>
+        <v>695953</v>
       </c>
       <c r="R49" t="n">
-        <v>6652356</v>
+        <v>6652663</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129096108</v>
+        <v>129096633</v>
       </c>
       <c r="B50" t="n">
-        <v>5177</v>
+        <v>100770</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>222771</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>695953</v>
+        <v>696078</v>
       </c>
       <c r="R50" t="n">
-        <v>6652663</v>
+        <v>6652601</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,32 +5728,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129096633</v>
+        <v>129097529</v>
       </c>
       <c r="B51" t="n">
-        <v>100763</v>
+        <v>91540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,10 +5763,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696078</v>
+        <v>696166</v>
       </c>
       <c r="R51" t="n">
-        <v>6652601</v>
+        <v>6652538</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5828,7 +5828,7 @@
         <v>129096360</v>
       </c>
       <c r="B52" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>129097801</v>
       </c>
       <c r="B53" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>129097202</v>
       </c>
       <c r="B54" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3698,7 +3698,7 @@
         <v>129095316</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>129096111</v>
       </c>
       <c r="B31" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129096950</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>129095299</v>
       </c>
       <c r="B33" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>129094741</v>
       </c>
       <c r="B34" t="n">
-        <v>87058</v>
+        <v>87060</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>91752</v>
+        <v>91754</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>105824</v>
+        <v>105826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>101769</v>
+        <v>101771</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>129096138</v>
       </c>
       <c r="B38" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>129095794</v>
       </c>
       <c r="B39" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>129095746</v>
       </c>
       <c r="B40" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>129096063</v>
       </c>
       <c r="B41" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>129095080</v>
       </c>
       <c r="B42" t="n">
-        <v>87058</v>
+        <v>87060</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>129097843</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5054,27 +5054,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129096022</v>
+        <v>129097563</v>
       </c>
       <c r="B44" t="n">
-        <v>91948</v>
+        <v>91754</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6040186</v>
+        <v>1106</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5084,10 +5089,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695988</v>
+        <v>696166</v>
       </c>
       <c r="R44" t="n">
-        <v>6652611</v>
+        <v>6652538</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5146,32 +5151,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129097563</v>
+        <v>129096022</v>
       </c>
       <c r="B45" t="n">
-        <v>91752</v>
+        <v>91950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1106</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Vågticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696166</v>
+        <v>695988</v>
       </c>
       <c r="R45" t="n">
-        <v>6652538</v>
+        <v>6652611</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5246,7 +5246,7 @@
         <v>129096736</v>
       </c>
       <c r="B46" t="n">
-        <v>96005</v>
+        <v>96007</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>129097597</v>
       </c>
       <c r="B47" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5437,32 +5437,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129097950</v>
+        <v>129097529</v>
       </c>
       <c r="B48" t="n">
-        <v>92478</v>
+        <v>91542</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696312</v>
+        <v>696166</v>
       </c>
       <c r="R48" t="n">
-        <v>6652356</v>
+        <v>6652538</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129096108</v>
+        <v>129097950</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>92480</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>4769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>695953</v>
+        <v>696312</v>
       </c>
       <c r="R49" t="n">
-        <v>6652663</v>
+        <v>6652356</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5634,7 +5634,7 @@
         <v>129096633</v>
       </c>
       <c r="B50" t="n">
-        <v>100770</v>
+        <v>100772</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5728,32 +5728,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129097529</v>
+        <v>129096360</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>100866</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,13 +5763,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696166</v>
+        <v>696042</v>
       </c>
       <c r="R51" t="n">
-        <v>6652538</v>
+        <v>6652606</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5825,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129096360</v>
+        <v>129096108</v>
       </c>
       <c r="B52" t="n">
-        <v>100864</v>
+        <v>5177</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,21 +5836,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5860,13 +5860,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696042</v>
+        <v>695953</v>
       </c>
       <c r="R52" t="n">
-        <v>6652606</v>
+        <v>6652663</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>129097801</v>
       </c>
       <c r="B53" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>129097202</v>
       </c>
       <c r="B54" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096138</v>
+        <v>129095794</v>
       </c>
       <c r="B38" t="n">
-        <v>91560</v>
+        <v>92873</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4487,21 +4487,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695953</v>
+        <v>695984</v>
       </c>
       <c r="R38" t="n">
-        <v>6652663</v>
+        <v>6652567</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,10 +4573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129095794</v>
+        <v>129096138</v>
       </c>
       <c r="B39" t="n">
-        <v>92873</v>
+        <v>91560</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4584,21 +4584,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695984</v>
+        <v>695953</v>
       </c>
       <c r="R39" t="n">
-        <v>6652567</v>
+        <v>6652663</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5437,32 +5437,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129097529</v>
+        <v>129096633</v>
       </c>
       <c r="B48" t="n">
-        <v>91542</v>
+        <v>100772</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696166</v>
+        <v>696078</v>
       </c>
       <c r="R48" t="n">
-        <v>6652538</v>
+        <v>6652601</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129097950</v>
+        <v>129096360</v>
       </c>
       <c r="B49" t="n">
-        <v>92480</v>
+        <v>100866</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,13 +5569,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696312</v>
+        <v>696042</v>
       </c>
       <c r="R49" t="n">
-        <v>6652356</v>
+        <v>6652606</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5631,32 +5631,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129096633</v>
+        <v>129097529</v>
       </c>
       <c r="B50" t="n">
-        <v>100772</v>
+        <v>91542</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696078</v>
+        <v>696166</v>
       </c>
       <c r="R50" t="n">
-        <v>6652601</v>
+        <v>6652538</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129096360</v>
+        <v>129097950</v>
       </c>
       <c r="B51" t="n">
-        <v>100866</v>
+        <v>92480</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,13 +5763,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696042</v>
+        <v>696312</v>
       </c>
       <c r="R51" t="n">
-        <v>6652606</v>
+        <v>6652356</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3986,48 +3986,47 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129095299</v>
+        <v>129094741</v>
       </c>
       <c r="B33" t="n">
-        <v>91997</v>
+        <v>87060</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>3624</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696057</v>
+        <v>696155</v>
       </c>
       <c r="R33" t="n">
-        <v>6652483</v>
+        <v>6652354</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4065,6 +4064,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4083,47 +4083,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129094741</v>
+        <v>129095299</v>
       </c>
       <c r="B34" t="n">
-        <v>87060</v>
+        <v>91997</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3624</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696155</v>
+        <v>696057</v>
       </c>
       <c r="R34" t="n">
-        <v>6652354</v>
+        <v>6652483</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4161,7 +4162,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5437,32 +5437,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129096633</v>
+        <v>129097529</v>
       </c>
       <c r="B48" t="n">
-        <v>100772</v>
+        <v>91542</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696078</v>
+        <v>696166</v>
       </c>
       <c r="R48" t="n">
-        <v>6652601</v>
+        <v>6652538</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129096360</v>
+        <v>129097950</v>
       </c>
       <c r="B49" t="n">
-        <v>100866</v>
+        <v>92480</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,13 +5569,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696042</v>
+        <v>696312</v>
       </c>
       <c r="R49" t="n">
-        <v>6652606</v>
+        <v>6652356</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5631,32 +5631,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129097529</v>
+        <v>129096633</v>
       </c>
       <c r="B50" t="n">
-        <v>91542</v>
+        <v>100772</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696166</v>
+        <v>696078</v>
       </c>
       <c r="R50" t="n">
-        <v>6652538</v>
+        <v>6652601</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129097950</v>
+        <v>129096360</v>
       </c>
       <c r="B51" t="n">
-        <v>92480</v>
+        <v>100866</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5739,21 +5739,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,13 +5763,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696312</v>
+        <v>696042</v>
       </c>
       <c r="R51" t="n">
-        <v>6652356</v>
+        <v>6652606</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3698,7 +3698,7 @@
         <v>129095316</v>
       </c>
       <c r="B30" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>129096111</v>
       </c>
       <c r="B31" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129096950</v>
       </c>
       <c r="B32" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3986,47 +3986,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129094741</v>
+        <v>129095299</v>
       </c>
       <c r="B33" t="n">
-        <v>87060</v>
+        <v>91992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3624</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696155</v>
+        <v>696057</v>
       </c>
       <c r="R33" t="n">
-        <v>6652354</v>
+        <v>6652483</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4064,7 +4065,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4083,48 +4083,47 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129095299</v>
+        <v>129094741</v>
       </c>
       <c r="B34" t="n">
-        <v>91997</v>
+        <v>87061</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>3624</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696057</v>
+        <v>696155</v>
       </c>
       <c r="R34" t="n">
-        <v>6652483</v>
+        <v>6652354</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4162,6 +4161,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>91754</v>
+        <v>91763</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>105826</v>
+        <v>105852</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>101771</v>
+        <v>101797</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129095794</v>
+        <v>129096138</v>
       </c>
       <c r="B38" t="n">
-        <v>92873</v>
+        <v>91558</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4487,21 +4487,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695984</v>
+        <v>695953</v>
       </c>
       <c r="R38" t="n">
-        <v>6652567</v>
+        <v>6652663</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,10 +4573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129096138</v>
+        <v>129095794</v>
       </c>
       <c r="B39" t="n">
-        <v>91560</v>
+        <v>92859</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4584,21 +4584,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695953</v>
+        <v>695984</v>
       </c>
       <c r="R39" t="n">
-        <v>6652663</v>
+        <v>6652567</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4673,7 +4673,7 @@
         <v>129095746</v>
       </c>
       <c r="B40" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>129096063</v>
       </c>
       <c r="B41" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>129095080</v>
       </c>
       <c r="B42" t="n">
-        <v>87060</v>
+        <v>87061</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>129097843</v>
       </c>
       <c r="B43" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5054,32 +5054,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129097563</v>
+        <v>129096022</v>
       </c>
       <c r="B44" t="n">
-        <v>91754</v>
+        <v>91958</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1106</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Vågticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5089,10 +5084,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696166</v>
+        <v>695988</v>
       </c>
       <c r="R44" t="n">
-        <v>6652538</v>
+        <v>6652611</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5151,27 +5146,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129096022</v>
+        <v>129097563</v>
       </c>
       <c r="B45" t="n">
-        <v>91950</v>
+        <v>91763</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6040186</v>
+        <v>1106</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695988</v>
+        <v>696166</v>
       </c>
       <c r="R45" t="n">
-        <v>6652611</v>
+        <v>6652538</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5246,7 +5246,7 @@
         <v>129096736</v>
       </c>
       <c r="B46" t="n">
-        <v>96007</v>
+        <v>96033</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>129097597</v>
       </c>
       <c r="B47" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5437,32 +5437,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129097529</v>
+        <v>129096633</v>
       </c>
       <c r="B48" t="n">
-        <v>91542</v>
+        <v>100798</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696166</v>
+        <v>696078</v>
       </c>
       <c r="R48" t="n">
-        <v>6652538</v>
+        <v>6652601</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129097950</v>
+        <v>129096108</v>
       </c>
       <c r="B49" t="n">
-        <v>92480</v>
+        <v>5177</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4769</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696312</v>
+        <v>695953</v>
       </c>
       <c r="R49" t="n">
-        <v>6652356</v>
+        <v>6652663</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129096633</v>
+        <v>129096360</v>
       </c>
       <c r="B50" t="n">
-        <v>100772</v>
+        <v>100892</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,13 +5666,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696078</v>
+        <v>696042</v>
       </c>
       <c r="R50" t="n">
-        <v>6652601</v>
+        <v>6652606</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5728,32 +5728,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129096360</v>
+        <v>129097529</v>
       </c>
       <c r="B51" t="n">
-        <v>100866</v>
+        <v>91540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,13 +5763,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696042</v>
+        <v>696166</v>
       </c>
       <c r="R51" t="n">
-        <v>6652606</v>
+        <v>6652538</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5825,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129096108</v>
+        <v>129097950</v>
       </c>
       <c r="B52" t="n">
-        <v>5177</v>
+        <v>92494</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,21 +5836,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>4769</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>695953</v>
+        <v>696312</v>
       </c>
       <c r="R52" t="n">
-        <v>6652663</v>
+        <v>6652356</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5925,7 +5925,7 @@
         <v>129097801</v>
       </c>
       <c r="B53" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5942,12 +5942,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6022,7 +6022,7 @@
         <v>129097202</v>
       </c>
       <c r="B54" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3989,7 +3989,7 @@
         <v>129095299</v>
       </c>
       <c r="B33" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>91763</v>
+        <v>91764</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096372</v>
+        <v>129097762</v>
       </c>
       <c r="B36" t="n">
-        <v>105852</v>
+        <v>101799</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4293,21 +4293,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4317,13 +4317,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696042</v>
+        <v>696154</v>
       </c>
       <c r="R36" t="n">
-        <v>6652606</v>
+        <v>6652433</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4379,10 +4379,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129097762</v>
+        <v>129096372</v>
       </c>
       <c r="B37" t="n">
-        <v>101797</v>
+        <v>105854</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221235</v>
+        <v>221423</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4414,13 +4414,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696154</v>
+        <v>696042</v>
       </c>
       <c r="R37" t="n">
-        <v>6652433</v>
+        <v>6652606</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>129096138</v>
       </c>
       <c r="B38" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4496,14 +4496,10 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4576,7 +4572,7 @@
         <v>129095794</v>
       </c>
       <c r="B39" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4673,7 +4669,7 @@
         <v>129095746</v>
       </c>
       <c r="B40" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,27 +5050,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129096022</v>
+        <v>129097563</v>
       </c>
       <c r="B44" t="n">
-        <v>91958</v>
+        <v>91764</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6040186</v>
+        <v>1106</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5084,10 +5085,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695988</v>
+        <v>696166</v>
       </c>
       <c r="R44" t="n">
-        <v>6652611</v>
+        <v>6652538</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5146,32 +5147,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129097563</v>
+        <v>129096022</v>
       </c>
       <c r="B45" t="n">
-        <v>91763</v>
+        <v>91959</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1106</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Vågticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5181,10 +5177,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696166</v>
+        <v>695988</v>
       </c>
       <c r="R45" t="n">
-        <v>6652538</v>
+        <v>6652611</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5246,7 +5242,7 @@
         <v>129096736</v>
       </c>
       <c r="B46" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5437,32 +5433,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129096633</v>
+        <v>129097529</v>
       </c>
       <c r="B48" t="n">
-        <v>100798</v>
+        <v>91540</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696078</v>
+        <v>696166</v>
       </c>
       <c r="R48" t="n">
-        <v>6652601</v>
+        <v>6652538</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5530,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129096108</v>
+        <v>129097950</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>92495</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5541,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>4769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5565,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>695953</v>
+        <v>696312</v>
       </c>
       <c r="R49" t="n">
-        <v>6652663</v>
+        <v>6652356</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5634,7 +5630,7 @@
         <v>129096360</v>
       </c>
       <c r="B50" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5728,32 +5724,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129097529</v>
+        <v>129096108</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>5177</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,10 +5759,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696166</v>
+        <v>695953</v>
       </c>
       <c r="R51" t="n">
-        <v>6652538</v>
+        <v>6652663</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,10 +5821,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129097950</v>
+        <v>129096633</v>
       </c>
       <c r="B52" t="n">
-        <v>92494</v>
+        <v>100799</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,21 +5832,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5860,10 +5856,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696312</v>
+        <v>696078</v>
       </c>
       <c r="R52" t="n">
-        <v>6652356</v>
+        <v>6652601</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5925,7 +5921,7 @@
         <v>129097801</v>
       </c>
       <c r="B53" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -4282,10 +4282,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129097762</v>
+        <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>101799</v>
+        <v>105855</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4293,21 +4293,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221235</v>
+        <v>221423</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4317,13 +4317,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696154</v>
+        <v>696042</v>
       </c>
       <c r="R36" t="n">
-        <v>6652433</v>
+        <v>6652606</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4379,10 +4379,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129096372</v>
+        <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>105854</v>
+        <v>101800</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4414,13 +4414,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696042</v>
+        <v>696154</v>
       </c>
       <c r="R37" t="n">
-        <v>6652606</v>
+        <v>6652433</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>129096736</v>
       </c>
       <c r="B46" t="n">
-        <v>96034</v>
+        <v>96035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129096360</v>
+        <v>129096108</v>
       </c>
       <c r="B50" t="n">
-        <v>100894</v>
+        <v>5177</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696042</v>
+        <v>695953</v>
       </c>
       <c r="R50" t="n">
-        <v>6652606</v>
+        <v>6652663</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129096108</v>
+        <v>129096633</v>
       </c>
       <c r="B51" t="n">
-        <v>5177</v>
+        <v>100800</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100526</v>
+        <v>222771</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>695953</v>
+        <v>696078</v>
       </c>
       <c r="R51" t="n">
-        <v>6652663</v>
+        <v>6652601</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129096633</v>
+        <v>129096360</v>
       </c>
       <c r="B52" t="n">
-        <v>100799</v>
+        <v>100895</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696078</v>
+        <v>696042</v>
       </c>
       <c r="R52" t="n">
-        <v>6652601</v>
+        <v>6652606</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3698,7 +3698,7 @@
         <v>129095316</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>129096111</v>
       </c>
       <c r="B31" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129096950</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>129095299</v>
       </c>
       <c r="B33" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>129094741</v>
       </c>
       <c r="B34" t="n">
-        <v>87061</v>
+        <v>87064</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>91764</v>
+        <v>91767</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>105855</v>
+        <v>105859</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>101800</v>
+        <v>101804</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096138</v>
+        <v>129095794</v>
       </c>
       <c r="B38" t="n">
-        <v>91560</v>
+        <v>92863</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4487,19 +4487,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4507,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695953</v>
+        <v>695984</v>
       </c>
       <c r="R38" t="n">
-        <v>6652663</v>
+        <v>6652567</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,10 +4573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129095794</v>
+        <v>129096138</v>
       </c>
       <c r="B39" t="n">
-        <v>92860</v>
+        <v>91563</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4580,23 +4584,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695984</v>
+        <v>695953</v>
       </c>
       <c r="R39" t="n">
-        <v>6652567</v>
+        <v>6652663</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,7 +4669,7 @@
         <v>129095746</v>
       </c>
       <c r="B40" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>129096063</v>
       </c>
       <c r="B41" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>129095080</v>
       </c>
       <c r="B42" t="n">
-        <v>87061</v>
+        <v>87064</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>129097843</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5050,32 +5050,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129097563</v>
+        <v>129096022</v>
       </c>
       <c r="B44" t="n">
-        <v>91764</v>
+        <v>91962</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1106</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Vågticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5085,10 +5080,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696166</v>
+        <v>695988</v>
       </c>
       <c r="R44" t="n">
-        <v>6652538</v>
+        <v>6652611</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5147,27 +5142,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129096022</v>
+        <v>129097563</v>
       </c>
       <c r="B45" t="n">
-        <v>91959</v>
+        <v>91767</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6040186</v>
+        <v>1106</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695988</v>
+        <v>696166</v>
       </c>
       <c r="R45" t="n">
-        <v>6652611</v>
+        <v>6652538</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5242,7 +5242,7 @@
         <v>129096736</v>
       </c>
       <c r="B46" t="n">
-        <v>96035</v>
+        <v>96039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>129097597</v>
       </c>
       <c r="B47" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5433,32 +5433,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129097529</v>
+        <v>129097950</v>
       </c>
       <c r="B48" t="n">
-        <v>91540</v>
+        <v>92498</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696166</v>
+        <v>696312</v>
       </c>
       <c r="R48" t="n">
-        <v>6652538</v>
+        <v>6652356</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5530,32 +5530,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129097950</v>
+        <v>129097529</v>
       </c>
       <c r="B49" t="n">
-        <v>92495</v>
+        <v>91543</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696312</v>
+        <v>696166</v>
       </c>
       <c r="R49" t="n">
-        <v>6652356</v>
+        <v>6652538</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5727,7 +5727,7 @@
         <v>129096633</v>
       </c>
       <c r="B51" t="n">
-        <v>100800</v>
+        <v>100804</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>129096360</v>
       </c>
       <c r="B52" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>129097801</v>
       </c>
       <c r="B53" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>129097202</v>
       </c>
       <c r="B54" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -5433,10 +5433,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129097950</v>
+        <v>129096108</v>
       </c>
       <c r="B48" t="n">
-        <v>92498</v>
+        <v>5177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4769</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696312</v>
+        <v>695953</v>
       </c>
       <c r="R48" t="n">
-        <v>6652356</v>
+        <v>6652663</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5530,32 +5530,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129097529</v>
+        <v>129096633</v>
       </c>
       <c r="B49" t="n">
-        <v>91543</v>
+        <v>100804</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696166</v>
+        <v>696078</v>
       </c>
       <c r="R49" t="n">
-        <v>6652538</v>
+        <v>6652601</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129096108</v>
+        <v>129096360</v>
       </c>
       <c r="B50" t="n">
-        <v>5177</v>
+        <v>100899</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>695953</v>
+        <v>696042</v>
       </c>
       <c r="R50" t="n">
-        <v>6652663</v>
+        <v>6652606</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129096633</v>
+        <v>129097529</v>
       </c>
       <c r="B51" t="n">
-        <v>100804</v>
+        <v>91543</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696078</v>
+        <v>696166</v>
       </c>
       <c r="R51" t="n">
-        <v>6652601</v>
+        <v>6652538</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129096360</v>
+        <v>129097950</v>
       </c>
       <c r="B52" t="n">
-        <v>100899</v>
+        <v>92498</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696042</v>
+        <v>696312</v>
       </c>
       <c r="R52" t="n">
-        <v>6652606</v>
+        <v>6652356</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3698,7 +3698,7 @@
         <v>129095316</v>
       </c>
       <c r="B30" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>129096111</v>
       </c>
       <c r="B31" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129096950</v>
       </c>
       <c r="B32" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3986,48 +3986,47 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129095299</v>
+        <v>129094741</v>
       </c>
       <c r="B33" t="n">
-        <v>91996</v>
+        <v>87066</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>3624</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696057</v>
+        <v>696155</v>
       </c>
       <c r="R33" t="n">
-        <v>6652483</v>
+        <v>6652354</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4065,6 +4064,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4083,47 +4083,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129094741</v>
+        <v>129095299</v>
       </c>
       <c r="B34" t="n">
-        <v>87064</v>
+        <v>91998</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3624</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696155</v>
+        <v>696057</v>
       </c>
       <c r="R34" t="n">
-        <v>6652354</v>
+        <v>6652483</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4161,7 +4162,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>91767</v>
+        <v>91769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>105859</v>
+        <v>105861</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>101804</v>
+        <v>101806</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129095794</v>
+        <v>129096138</v>
       </c>
       <c r="B38" t="n">
-        <v>92863</v>
+        <v>91565</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4487,23 +4487,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4511,10 +4507,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695984</v>
+        <v>695953</v>
       </c>
       <c r="R38" t="n">
-        <v>6652567</v>
+        <v>6652663</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129096138</v>
+        <v>129095794</v>
       </c>
       <c r="B39" t="n">
-        <v>91563</v>
+        <v>92865</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4584,19 +4580,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695953</v>
+        <v>695984</v>
       </c>
       <c r="R39" t="n">
-        <v>6652663</v>
+        <v>6652567</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,7 +4669,7 @@
         <v>129095746</v>
       </c>
       <c r="B40" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>129096063</v>
       </c>
       <c r="B41" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>129095080</v>
       </c>
       <c r="B42" t="n">
-        <v>87064</v>
+        <v>87066</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>129097843</v>
       </c>
       <c r="B43" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>129096022</v>
       </c>
       <c r="B44" t="n">
-        <v>91962</v>
+        <v>91964</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>129097563</v>
       </c>
       <c r="B45" t="n">
-        <v>91767</v>
+        <v>91769</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>129096736</v>
       </c>
       <c r="B46" t="n">
-        <v>96039</v>
+        <v>96041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>129097597</v>
       </c>
       <c r="B47" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>129096633</v>
       </c>
       <c r="B49" t="n">
-        <v>100804</v>
+        <v>100806</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>129096360</v>
       </c>
       <c r="B50" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129097529</v>
+        <v>129097950</v>
       </c>
       <c r="B51" t="n">
-        <v>91543</v>
+        <v>92500</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696166</v>
+        <v>696312</v>
       </c>
       <c r="R51" t="n">
-        <v>6652538</v>
+        <v>6652356</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,32 +5821,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129097950</v>
+        <v>129097529</v>
       </c>
       <c r="B52" t="n">
-        <v>92498</v>
+        <v>91545</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696312</v>
+        <v>696166</v>
       </c>
       <c r="R52" t="n">
-        <v>6652356</v>
+        <v>6652538</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
         <v>129097801</v>
       </c>
       <c r="B53" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>129097202</v>
       </c>
       <c r="B54" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3698,7 +3698,7 @@
         <v>129095316</v>
       </c>
       <c r="B30" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>129096111</v>
       </c>
       <c r="B31" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129096950</v>
       </c>
       <c r="B32" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3986,47 +3986,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129094741</v>
+        <v>129095299</v>
       </c>
       <c r="B33" t="n">
-        <v>87066</v>
+        <v>92002</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3624</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696155</v>
+        <v>696057</v>
       </c>
       <c r="R33" t="n">
-        <v>6652354</v>
+        <v>6652483</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4064,7 +4065,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4083,48 +4083,47 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129095299</v>
+        <v>129094741</v>
       </c>
       <c r="B34" t="n">
-        <v>91998</v>
+        <v>87070</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>3624</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696057</v>
+        <v>696155</v>
       </c>
       <c r="R34" t="n">
-        <v>6652483</v>
+        <v>6652354</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4162,6 +4161,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>91769</v>
+        <v>91773</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>105861</v>
+        <v>105865</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>101806</v>
+        <v>101810</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>129096138</v>
       </c>
       <c r="B38" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>129095794</v>
       </c>
       <c r="B39" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>129095746</v>
       </c>
       <c r="B40" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>129096063</v>
       </c>
       <c r="B41" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>129095080</v>
       </c>
       <c r="B42" t="n">
-        <v>87066</v>
+        <v>87070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>129097843</v>
       </c>
       <c r="B43" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5050,27 +5050,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129096022</v>
+        <v>129097563</v>
       </c>
       <c r="B44" t="n">
-        <v>91964</v>
+        <v>91773</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6040186</v>
+        <v>1106</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5080,10 +5085,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695988</v>
+        <v>696166</v>
       </c>
       <c r="R44" t="n">
-        <v>6652611</v>
+        <v>6652538</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5142,32 +5147,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129097563</v>
+        <v>129096022</v>
       </c>
       <c r="B45" t="n">
-        <v>91769</v>
+        <v>91968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1106</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Vågticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696166</v>
+        <v>695988</v>
       </c>
       <c r="R45" t="n">
-        <v>6652538</v>
+        <v>6652611</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5242,7 +5242,7 @@
         <v>129096736</v>
       </c>
       <c r="B46" t="n">
-        <v>96041</v>
+        <v>96045</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>129097597</v>
       </c>
       <c r="B47" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129096108</v>
+        <v>129096633</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>100810</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>222771</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>695953</v>
+        <v>696078</v>
       </c>
       <c r="R48" t="n">
-        <v>6652663</v>
+        <v>6652601</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129096633</v>
+        <v>129096360</v>
       </c>
       <c r="B49" t="n">
-        <v>100806</v>
+        <v>100905</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5565,13 +5565,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696078</v>
+        <v>696042</v>
       </c>
       <c r="R49" t="n">
-        <v>6652601</v>
+        <v>6652606</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129096360</v>
+        <v>129097529</v>
       </c>
       <c r="B50" t="n">
-        <v>100901</v>
+        <v>91549</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696042</v>
+        <v>696166</v>
       </c>
       <c r="R50" t="n">
-        <v>6652606</v>
+        <v>6652538</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>129097950</v>
       </c>
       <c r="B51" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5821,32 +5821,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129097529</v>
+        <v>129096108</v>
       </c>
       <c r="B52" t="n">
-        <v>91545</v>
+        <v>5177</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696166</v>
+        <v>695953</v>
       </c>
       <c r="R52" t="n">
-        <v>6652538</v>
+        <v>6652663</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
         <v>129097801</v>
       </c>
       <c r="B53" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>129097202</v>
       </c>
       <c r="B54" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3698,7 +3698,7 @@
         <v>129095316</v>
       </c>
       <c r="B30" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>129096111</v>
       </c>
       <c r="B31" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129096950</v>
       </c>
       <c r="B32" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>129095299</v>
       </c>
       <c r="B33" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>129094741</v>
       </c>
       <c r="B34" t="n">
-        <v>87070</v>
+        <v>87071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>91773</v>
+        <v>91774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>105865</v>
+        <v>105875</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>101810</v>
+        <v>101820</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096138</v>
+        <v>129095794</v>
       </c>
       <c r="B38" t="n">
-        <v>91569</v>
+        <v>92870</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4487,19 +4487,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4507,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695953</v>
+        <v>695984</v>
       </c>
       <c r="R38" t="n">
-        <v>6652663</v>
+        <v>6652567</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,10 +4573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129095794</v>
+        <v>129096138</v>
       </c>
       <c r="B39" t="n">
-        <v>92869</v>
+        <v>91570</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4580,23 +4584,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695984</v>
+        <v>695953</v>
       </c>
       <c r="R39" t="n">
-        <v>6652567</v>
+        <v>6652663</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,7 +4669,7 @@
         <v>129095746</v>
       </c>
       <c r="B40" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>129096063</v>
       </c>
       <c r="B41" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>129095080</v>
       </c>
       <c r="B42" t="n">
-        <v>87070</v>
+        <v>87071</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>129097843</v>
       </c>
       <c r="B43" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>129097563</v>
       </c>
       <c r="B44" t="n">
-        <v>91773</v>
+        <v>91774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>129096022</v>
       </c>
       <c r="B45" t="n">
-        <v>91968</v>
+        <v>91969</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>129096736</v>
       </c>
       <c r="B46" t="n">
-        <v>96045</v>
+        <v>96053</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>129097597</v>
       </c>
       <c r="B47" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129096633</v>
+        <v>129096108</v>
       </c>
       <c r="B48" t="n">
-        <v>100810</v>
+        <v>5177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222771</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696078</v>
+        <v>695953</v>
       </c>
       <c r="R48" t="n">
-        <v>6652601</v>
+        <v>6652663</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5533,7 +5533,7 @@
         <v>129096360</v>
       </c>
       <c r="B49" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>129097529</v>
       </c>
       <c r="B50" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>129097950</v>
       </c>
       <c r="B51" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129096108</v>
+        <v>129096633</v>
       </c>
       <c r="B52" t="n">
-        <v>5177</v>
+        <v>100818</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>222771</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>695953</v>
+        <v>696078</v>
       </c>
       <c r="R52" t="n">
-        <v>6652663</v>
+        <v>6652601</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
         <v>129097801</v>
       </c>
       <c r="B53" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>129097202</v>
       </c>
       <c r="B54" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -5433,10 +5433,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129096108</v>
+        <v>129096633</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>100818</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>222771</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>695953</v>
+        <v>696078</v>
       </c>
       <c r="R48" t="n">
-        <v>6652663</v>
+        <v>6652601</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5530,32 +5530,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129096360</v>
+        <v>129097529</v>
       </c>
       <c r="B49" t="n">
-        <v>100913</v>
+        <v>91550</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5565,13 +5565,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696042</v>
+        <v>696166</v>
       </c>
       <c r="R49" t="n">
-        <v>6652606</v>
+        <v>6652538</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129097529</v>
+        <v>129096108</v>
       </c>
       <c r="B50" t="n">
-        <v>91550</v>
+        <v>5177</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696166</v>
+        <v>695953</v>
       </c>
       <c r="R50" t="n">
-        <v>6652538</v>
+        <v>6652663</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129096633</v>
+        <v>129096360</v>
       </c>
       <c r="B52" t="n">
-        <v>100818</v>
+        <v>100913</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696078</v>
+        <v>696042</v>
       </c>
       <c r="R52" t="n">
-        <v>6652601</v>
+        <v>6652606</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3698,7 +3698,7 @@
         <v>129095316</v>
       </c>
       <c r="B30" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>129096111</v>
       </c>
       <c r="B31" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129096950</v>
       </c>
       <c r="B32" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>129095299</v>
       </c>
       <c r="B33" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>91774</v>
+        <v>91777</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>105875</v>
+        <v>105878</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>101820</v>
+        <v>101823</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129095794</v>
+        <v>129096138</v>
       </c>
       <c r="B38" t="n">
-        <v>92870</v>
+        <v>91573</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4487,23 +4487,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4511,10 +4507,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695984</v>
+        <v>695953</v>
       </c>
       <c r="R38" t="n">
-        <v>6652567</v>
+        <v>6652663</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129096138</v>
+        <v>129095794</v>
       </c>
       <c r="B39" t="n">
-        <v>91570</v>
+        <v>92873</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4584,19 +4580,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695953</v>
+        <v>695984</v>
       </c>
       <c r="R39" t="n">
-        <v>6652663</v>
+        <v>6652567</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4669,7 +4669,7 @@
         <v>129095746</v>
       </c>
       <c r="B40" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>129096063</v>
       </c>
       <c r="B41" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>129097843</v>
       </c>
       <c r="B43" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>129097563</v>
       </c>
       <c r="B44" t="n">
-        <v>91774</v>
+        <v>91777</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>129096022</v>
       </c>
       <c r="B45" t="n">
-        <v>91969</v>
+        <v>91972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>129096736</v>
       </c>
       <c r="B46" t="n">
-        <v>96053</v>
+        <v>96056</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>129097597</v>
       </c>
       <c r="B47" t="n">
-        <v>91564</v>
+        <v>91567</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5433,32 +5433,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129096633</v>
+        <v>129097529</v>
       </c>
       <c r="B48" t="n">
-        <v>100818</v>
+        <v>91553</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696078</v>
+        <v>696166</v>
       </c>
       <c r="R48" t="n">
-        <v>6652601</v>
+        <v>6652538</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5530,32 +5530,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129097529</v>
+        <v>129097950</v>
       </c>
       <c r="B49" t="n">
-        <v>91550</v>
+        <v>92508</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696166</v>
+        <v>696312</v>
       </c>
       <c r="R49" t="n">
-        <v>6652538</v>
+        <v>6652356</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129097950</v>
+        <v>129096633</v>
       </c>
       <c r="B51" t="n">
-        <v>92505</v>
+        <v>100821</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696312</v>
+        <v>696078</v>
       </c>
       <c r="R51" t="n">
-        <v>6652356</v>
+        <v>6652601</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5824,7 +5824,7 @@
         <v>129096360</v>
       </c>
       <c r="B52" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>129097801</v>
       </c>
       <c r="B53" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>129097202</v>
       </c>
       <c r="B54" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3986,48 +3986,47 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129095299</v>
+        <v>129094741</v>
       </c>
       <c r="B33" t="n">
-        <v>92006</v>
+        <v>87071</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>3624</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696057</v>
+        <v>696155</v>
       </c>
       <c r="R33" t="n">
-        <v>6652483</v>
+        <v>6652354</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4065,6 +4064,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4083,47 +4083,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129094741</v>
+        <v>129095299</v>
       </c>
       <c r="B34" t="n">
-        <v>87071</v>
+        <v>92006</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3624</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696155</v>
+        <v>696057</v>
       </c>
       <c r="R34" t="n">
-        <v>6652354</v>
+        <v>6652483</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4161,7 +4162,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4180,32 +4180,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129097381</v>
+        <v>129096372</v>
       </c>
       <c r="B35" t="n">
-        <v>91777</v>
+        <v>105878</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1106</v>
+        <v>221423</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696125</v>
+        <v>696042</v>
       </c>
       <c r="R35" t="n">
-        <v>6652488</v>
+        <v>6652606</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4251,11 +4251,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4282,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096372</v>
+        <v>129097762</v>
       </c>
       <c r="B36" t="n">
-        <v>105878</v>
+        <v>101823</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4293,21 +4288,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4317,13 +4312,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696042</v>
+        <v>696154</v>
       </c>
       <c r="R36" t="n">
-        <v>6652606</v>
+        <v>6652433</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4379,32 +4374,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129097762</v>
+        <v>129097381</v>
       </c>
       <c r="B37" t="n">
-        <v>101823</v>
+        <v>91777</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221235</v>
+        <v>1106</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4414,13 +4409,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696154</v>
+        <v>696125</v>
       </c>
       <c r="R37" t="n">
-        <v>6652433</v>
+        <v>6652488</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4450,6 +4445,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129096138</v>
+        <v>129095794</v>
       </c>
       <c r="B38" t="n">
-        <v>91573</v>
+        <v>92873</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4487,19 +4487,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4507,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695953</v>
+        <v>695984</v>
       </c>
       <c r="R38" t="n">
-        <v>6652663</v>
+        <v>6652567</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,10 +4573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129095794</v>
+        <v>129096138</v>
       </c>
       <c r="B39" t="n">
-        <v>92873</v>
+        <v>91573</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4580,23 +4584,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695984</v>
+        <v>695953</v>
       </c>
       <c r="R39" t="n">
-        <v>6652567</v>
+        <v>6652663</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5433,32 +5433,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129097529</v>
+        <v>129096108</v>
       </c>
       <c r="B48" t="n">
-        <v>91553</v>
+        <v>5177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696166</v>
+        <v>695953</v>
       </c>
       <c r="R48" t="n">
-        <v>6652538</v>
+        <v>6652663</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129097950</v>
+        <v>129096633</v>
       </c>
       <c r="B49" t="n">
-        <v>92508</v>
+        <v>100821</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696312</v>
+        <v>696078</v>
       </c>
       <c r="R49" t="n">
-        <v>6652356</v>
+        <v>6652601</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129096108</v>
+        <v>129096360</v>
       </c>
       <c r="B50" t="n">
-        <v>5177</v>
+        <v>100916</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>695953</v>
+        <v>696042</v>
       </c>
       <c r="R50" t="n">
-        <v>6652663</v>
+        <v>6652606</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129096633</v>
+        <v>129097950</v>
       </c>
       <c r="B51" t="n">
-        <v>100821</v>
+        <v>92508</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696078</v>
+        <v>696312</v>
       </c>
       <c r="R51" t="n">
-        <v>6652601</v>
+        <v>6652356</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,32 +5821,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129096360</v>
+        <v>129097529</v>
       </c>
       <c r="B52" t="n">
-        <v>100916</v>
+        <v>91553</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696042</v>
+        <v>696166</v>
       </c>
       <c r="R52" t="n">
-        <v>6652606</v>
+        <v>6652538</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -4180,32 +4180,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129096372</v>
+        <v>129097381</v>
       </c>
       <c r="B35" t="n">
-        <v>105878</v>
+        <v>91777</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221423</v>
+        <v>1106</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696042</v>
+        <v>696125</v>
       </c>
       <c r="R35" t="n">
-        <v>6652606</v>
+        <v>6652488</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4251,6 +4251,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4277,10 +4282,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129097762</v>
+        <v>129096372</v>
       </c>
       <c r="B36" t="n">
-        <v>101823</v>
+        <v>105878</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,21 +4293,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221235</v>
+        <v>221423</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4312,13 +4317,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696154</v>
+        <v>696042</v>
       </c>
       <c r="R36" t="n">
-        <v>6652433</v>
+        <v>6652606</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4374,32 +4379,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129097381</v>
+        <v>129097762</v>
       </c>
       <c r="B37" t="n">
-        <v>91777</v>
+        <v>101823</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1106</v>
+        <v>221235</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4409,13 +4414,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696125</v>
+        <v>696154</v>
       </c>
       <c r="R37" t="n">
-        <v>6652488</v>
+        <v>6652433</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4445,11 +4450,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5433,32 +5433,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129096108</v>
+        <v>129097529</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>91553</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>695953</v>
+        <v>696166</v>
       </c>
       <c r="R48" t="n">
-        <v>6652663</v>
+        <v>6652538</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129096633</v>
+        <v>129097950</v>
       </c>
       <c r="B49" t="n">
-        <v>100821</v>
+        <v>92508</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696078</v>
+        <v>696312</v>
       </c>
       <c r="R49" t="n">
-        <v>6652601</v>
+        <v>6652356</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129096360</v>
+        <v>129096108</v>
       </c>
       <c r="B50" t="n">
-        <v>100916</v>
+        <v>5177</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696042</v>
+        <v>695953</v>
       </c>
       <c r="R50" t="n">
-        <v>6652606</v>
+        <v>6652663</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129097950</v>
+        <v>129096633</v>
       </c>
       <c r="B51" t="n">
-        <v>92508</v>
+        <v>100821</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696312</v>
+        <v>696078</v>
       </c>
       <c r="R51" t="n">
-        <v>6652356</v>
+        <v>6652601</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,32 +5821,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129097529</v>
+        <v>129096360</v>
       </c>
       <c r="B52" t="n">
-        <v>91553</v>
+        <v>100916</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696166</v>
+        <v>696042</v>
       </c>
       <c r="R52" t="n">
-        <v>6652538</v>
+        <v>6652606</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -3986,47 +3986,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129094741</v>
+        <v>129095299</v>
       </c>
       <c r="B33" t="n">
-        <v>87071</v>
+        <v>92006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3624</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696155</v>
+        <v>696057</v>
       </c>
       <c r="R33" t="n">
-        <v>6652354</v>
+        <v>6652483</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4064,7 +4065,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4083,48 +4083,47 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129095299</v>
+        <v>129094741</v>
       </c>
       <c r="B34" t="n">
-        <v>92006</v>
+        <v>87071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>3624</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mossbottnarna, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696057</v>
+        <v>696155</v>
       </c>
       <c r="R34" t="n">
-        <v>6652483</v>
+        <v>6652354</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4162,6 +4161,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5433,32 +5433,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129097529</v>
+        <v>129096633</v>
       </c>
       <c r="B48" t="n">
-        <v>91553</v>
+        <v>100821</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696166</v>
+        <v>696078</v>
       </c>
       <c r="R48" t="n">
-        <v>6652538</v>
+        <v>6652601</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129097950</v>
+        <v>129096360</v>
       </c>
       <c r="B49" t="n">
-        <v>92508</v>
+        <v>100916</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5565,13 +5565,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696312</v>
+        <v>696042</v>
       </c>
       <c r="R49" t="n">
-        <v>6652356</v>
+        <v>6652606</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5627,10 +5627,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129096108</v>
+        <v>129097950</v>
       </c>
       <c r="B50" t="n">
-        <v>5177</v>
+        <v>92508</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5638,21 +5638,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>4769</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>695953</v>
+        <v>696312</v>
       </c>
       <c r="R50" t="n">
-        <v>6652663</v>
+        <v>6652356</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129096633</v>
+        <v>129097529</v>
       </c>
       <c r="B51" t="n">
-        <v>100821</v>
+        <v>91553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696078</v>
+        <v>696166</v>
       </c>
       <c r="R51" t="n">
-        <v>6652601</v>
+        <v>6652538</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129096360</v>
+        <v>129096108</v>
       </c>
       <c r="B52" t="n">
-        <v>100916</v>
+        <v>5177</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696042</v>
+        <v>695953</v>
       </c>
       <c r="R52" t="n">
-        <v>6652606</v>
+        <v>6652663</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -4180,32 +4180,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129097381</v>
+        <v>129096372</v>
       </c>
       <c r="B35" t="n">
-        <v>91777</v>
+        <v>105878</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1106</v>
+        <v>221423</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696125</v>
+        <v>696042</v>
       </c>
       <c r="R35" t="n">
-        <v>6652488</v>
+        <v>6652606</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4251,11 +4251,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4282,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129096372</v>
+        <v>129097762</v>
       </c>
       <c r="B36" t="n">
-        <v>105878</v>
+        <v>101823</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4293,21 +4288,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4317,13 +4312,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696042</v>
+        <v>696154</v>
       </c>
       <c r="R36" t="n">
-        <v>6652606</v>
+        <v>6652433</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4379,32 +4374,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129097762</v>
+        <v>129097381</v>
       </c>
       <c r="B37" t="n">
-        <v>101823</v>
+        <v>91777</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221235</v>
+        <v>1106</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4414,13 +4409,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696154</v>
+        <v>696125</v>
       </c>
       <c r="R37" t="n">
-        <v>6652433</v>
+        <v>6652488</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4450,6 +4445,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Stora kantiga porer</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129095794</v>
+        <v>129096138</v>
       </c>
       <c r="B38" t="n">
-        <v>92873</v>
+        <v>91573</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4487,23 +4487,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4511,10 +4507,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695984</v>
+        <v>695953</v>
       </c>
       <c r="R38" t="n">
-        <v>6652567</v>
+        <v>6652663</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129096138</v>
+        <v>129095794</v>
       </c>
       <c r="B39" t="n">
-        <v>91573</v>
+        <v>92873</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4584,19 +4580,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695953</v>
+        <v>695984</v>
       </c>
       <c r="R39" t="n">
-        <v>6652663</v>
+        <v>6652567</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5530,32 +5530,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129096360</v>
+        <v>129097529</v>
       </c>
       <c r="B49" t="n">
-        <v>100916</v>
+        <v>91553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5565,13 +5565,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696042</v>
+        <v>696166</v>
       </c>
       <c r="R49" t="n">
-        <v>6652606</v>
+        <v>6652538</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5724,32 +5724,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129097529</v>
+        <v>129096108</v>
       </c>
       <c r="B51" t="n">
-        <v>91553</v>
+        <v>5177</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696166</v>
+        <v>695953</v>
       </c>
       <c r="R51" t="n">
-        <v>6652538</v>
+        <v>6652663</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129096108</v>
+        <v>129096360</v>
       </c>
       <c r="B52" t="n">
-        <v>5177</v>
+        <v>100916</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>695953</v>
+        <v>696042</v>
       </c>
       <c r="R52" t="n">
-        <v>6652663</v>
+        <v>6652606</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -6115,7 +6115,7 @@
         <v>131084967</v>
       </c>
       <c r="B55" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6115,7 +6115,7 @@
         <v>131084967</v>
       </c>
       <c r="B55" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6226,6 +6226,213 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131431246</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92471</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Åla, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>696546</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6652082</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Observatör: Ulf Birgersson</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>131431247</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Åla, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>696074</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6652545</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristina Jiselmark</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -6232,7 +6232,7 @@
         <v>131431246</v>
       </c>
       <c r="B56" t="n">
-        <v>92476</v>
+        <v>92482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>131431247</v>
       </c>
       <c r="B57" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -6232,7 +6232,7 @@
         <v>131431246</v>
       </c>
       <c r="B56" t="n">
-        <v>92482</v>
+        <v>92483</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>131431247</v>
       </c>
       <c r="B57" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -6232,7 +6232,7 @@
         <v>131431246</v>
       </c>
       <c r="B56" t="n">
-        <v>92483</v>
+        <v>92484</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>131431247</v>
       </c>
       <c r="B57" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -6232,7 +6232,7 @@
         <v>131431246</v>
       </c>
       <c r="B56" t="n">
-        <v>92484</v>
+        <v>92487</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>131431247</v>
       </c>
       <c r="B57" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 24692-2025 artfynd.xlsx
+++ b/artfynd/A 24692-2025 artfynd.xlsx
@@ -6232,7 +6232,7 @@
         <v>131431246</v>
       </c>
       <c r="B56" t="n">
-        <v>92487</v>
+        <v>92493</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>131431247</v>
       </c>
       <c r="B57" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
